--- a/seo/backlinks-lasclay-audit.xlsx
+++ b/seo/backlinks-lasclay-audit.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Pistes à vérifier" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunités'!$A$4:$U$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunités'!$A$4:$U$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Pistes à vérifier'!$A$4:$H$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -144,8 +144,14 @@
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -191,8 +197,23 @@
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -215,6 +236,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -226,7 +261,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -404,6 +439,36 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1438,7 +1503,7 @@
     </row>
     <row r="11" ht="61.5" customHeight="1" s="29">
       <c r="A11" s="33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" s="34">
         <f>SUM(N11:Q11)</f>
@@ -1534,7 +1599,7 @@
     </row>
     <row r="12" ht="61.5" customHeight="1" s="29">
       <c r="A12" s="33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" s="34">
         <f>SUM(N12:Q12)</f>
@@ -1630,7 +1695,7 @@
     </row>
     <row r="13" ht="61.5" customHeight="1" s="29">
       <c r="A13" s="33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13" s="34">
         <f>SUM(N13:Q13)</f>
@@ -1726,7 +1791,7 @@
     </row>
     <row r="14" ht="61.5" customHeight="1" s="29">
       <c r="A14" s="33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14" s="34">
         <f>SUM(N14:Q14)</f>
@@ -1818,7 +1883,7 @@
     </row>
     <row r="15" ht="61.5" customHeight="1" s="29">
       <c r="A15" s="33" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15" s="34">
         <f>SUM(N15:Q15)</f>
@@ -1914,7 +1979,7 @@
     </row>
     <row r="16" ht="61.5" customHeight="1" s="29">
       <c r="A16" s="33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" s="34">
         <f>SUM(N16:Q16)</f>
@@ -2010,7 +2075,7 @@
     </row>
     <row r="17" ht="61.5" customHeight="1" s="29">
       <c r="A17" s="33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" s="34">
         <f>SUM(N17:Q17)</f>
@@ -2106,7 +2171,7 @@
     </row>
     <row r="18" ht="61.5" customHeight="1" s="29">
       <c r="A18" s="33" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" s="34">
         <f>SUM(N18:Q18)</f>
@@ -2198,7 +2263,7 @@
     </row>
     <row r="19" ht="61.5" customHeight="1" s="29">
       <c r="A19" s="33" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B19" s="34">
         <f>SUM(N19:Q19)</f>
@@ -2294,7 +2359,7 @@
     </row>
     <row r="20" ht="61.5" customHeight="1" s="29">
       <c r="A20" s="33" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B20" s="34">
         <f>SUM(N20:Q20)</f>
@@ -2390,7 +2455,7 @@
     </row>
     <row r="21" ht="61.5" customHeight="1" s="29">
       <c r="A21" s="33" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B21" s="34">
         <f>SUM(N21:Q21)</f>
@@ -2486,7 +2551,7 @@
     </row>
     <row r="22" ht="61.5" customHeight="1" s="29">
       <c r="A22" s="33" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B22" s="34">
         <f>SUM(N22:Q22)</f>
@@ -2582,7 +2647,7 @@
     </row>
     <row r="23" ht="61.5" customHeight="1" s="29">
       <c r="A23" s="33" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B23" s="34">
         <f>SUM(N23:Q23)</f>
@@ -2678,7 +2743,7 @@
     </row>
     <row r="24" ht="61.5" customHeight="1" s="29">
       <c r="A24" s="33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B24" s="34">
         <f>SUM(N24:Q24)</f>
@@ -2774,7 +2839,7 @@
     </row>
     <row r="25" ht="61.5" customHeight="1" s="29">
       <c r="A25" s="33" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B25" s="34">
         <f>SUM(N25:Q25)</f>
@@ -2870,7 +2935,7 @@
     </row>
     <row r="26" ht="61.5" customHeight="1" s="29">
       <c r="A26" s="43" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B26" s="44">
         <f>SUM(N26:Q26)</f>
@@ -2966,7 +3031,7 @@
     </row>
     <row r="27" ht="61.5" customHeight="1" s="29">
       <c r="A27" s="43" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B27" s="44">
         <f>SUM(N27:Q27)</f>
@@ -3062,7 +3127,7 @@
     </row>
     <row r="28" ht="61.5" customHeight="1" s="29">
       <c r="A28" s="43" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B28" s="44">
         <f>SUM(N28:Q28)</f>
@@ -3154,7 +3219,7 @@
     </row>
     <row r="29" ht="61.5" customHeight="1" s="29">
       <c r="A29" s="43" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B29" s="44">
         <f>SUM(N29:Q29)</f>
@@ -3246,7 +3311,7 @@
     </row>
     <row r="30" ht="61.5" customHeight="1" s="29">
       <c r="A30" s="43" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B30" s="44">
         <f>SUM(N30:Q30)</f>
@@ -3342,7 +3407,7 @@
     </row>
     <row r="31" ht="61.5" customHeight="1" s="29">
       <c r="A31" s="43" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B31" s="44">
         <f>SUM(N31:Q31)</f>
@@ -3438,7 +3503,7 @@
     </row>
     <row r="32" ht="61.5" customHeight="1" s="29">
       <c r="A32" s="43" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B32" s="44">
         <f>SUM(N32:Q32)</f>
@@ -3530,7 +3595,7 @@
     </row>
     <row r="33" ht="61.5" customHeight="1" s="29">
       <c r="A33" s="43" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B33" s="44">
         <f>SUM(N33:Q33)</f>
@@ -3626,7 +3691,7 @@
     </row>
     <row r="34" ht="61.5" customHeight="1" s="29">
       <c r="A34" s="43" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B34" s="44">
         <f>SUM(N34:Q34)</f>
@@ -3722,7 +3787,7 @@
     </row>
     <row r="35" ht="61.5" customHeight="1" s="29">
       <c r="A35" s="43" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B35" s="44">
         <f>SUM(N35:Q35)</f>
@@ -3818,7 +3883,7 @@
     </row>
     <row r="36" ht="61.5" customHeight="1" s="29">
       <c r="A36" s="43" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B36" s="44">
         <f>SUM(N36:Q36)</f>
@@ -3910,7 +3975,7 @@
     </row>
     <row r="37" ht="61.5" customHeight="1" s="29">
       <c r="A37" s="43" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B37" s="44">
         <f>SUM(N37:Q37)</f>
@@ -4006,7 +4071,7 @@
     </row>
     <row r="38" ht="61.5" customHeight="1" s="29">
       <c r="A38" s="43" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B38" s="44">
         <f>SUM(N38:Q38)</f>
@@ -4102,7 +4167,7 @@
     </row>
     <row r="39" ht="61.5" customHeight="1" s="29">
       <c r="A39" s="43" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B39" s="44">
         <f>SUM(N39:Q39)</f>
@@ -4198,7 +4263,7 @@
     </row>
     <row r="40" ht="61.5" customHeight="1" s="29">
       <c r="A40" s="43" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B40" s="44">
         <f>SUM(N40:Q40)</f>
@@ -4294,7 +4359,7 @@
     </row>
     <row r="41" ht="61.5" customHeight="1" s="29">
       <c r="A41" s="43" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B41" s="44">
         <f>SUM(N41:Q41)</f>
@@ -4390,7 +4455,7 @@
     </row>
     <row r="42" ht="61.5" customHeight="1" s="29">
       <c r="A42" s="43" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B42" s="44">
         <f>SUM(N42:Q42)</f>
@@ -4486,7 +4551,7 @@
     </row>
     <row r="43" ht="61.5" customHeight="1" s="29">
       <c r="A43" s="43" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B43" s="44">
         <f>SUM(N43:Q43)</f>
@@ -4582,7 +4647,7 @@
     </row>
     <row r="44" ht="61.5" customHeight="1" s="29">
       <c r="A44" s="43" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B44" s="44">
         <f>SUM(N44:Q44)</f>
@@ -4678,7 +4743,7 @@
     </row>
     <row r="45" ht="61.5" customHeight="1" s="29">
       <c r="A45" s="43" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B45" s="44">
         <f>SUM(N45:Q45)</f>
@@ -4774,7 +4839,7 @@
     </row>
     <row r="46" ht="61.5" customHeight="1" s="29">
       <c r="A46" s="43" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B46" s="44">
         <f>SUM(N46:Q46)</f>
@@ -4870,7 +4935,7 @@
     </row>
     <row r="47" ht="61.5" customHeight="1" s="29">
       <c r="A47" s="43" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B47" s="44">
         <f>SUM(N47:Q47)</f>
@@ -4966,7 +5031,7 @@
     </row>
     <row r="48" ht="61.5" customHeight="1" s="29">
       <c r="A48" s="43" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B48" s="44">
         <f>SUM(N48:Q48)</f>
@@ -5062,7 +5127,7 @@
     </row>
     <row r="49" ht="61.5" customHeight="1" s="29">
       <c r="A49" s="43" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B49" s="44">
         <f>SUM(N49:Q49)</f>
@@ -5158,7 +5223,7 @@
     </row>
     <row r="50" ht="61.5" customHeight="1" s="29">
       <c r="A50" s="43" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B50" s="44">
         <f>SUM(N50:Q50)</f>
@@ -5254,7 +5319,7 @@
     </row>
     <row r="51" ht="61.5" customHeight="1" s="29">
       <c r="A51" s="43" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B51" s="44">
         <f>SUM(N51:Q51)</f>
@@ -5350,7 +5415,7 @@
     </row>
     <row r="52" ht="61.5" customHeight="1" s="29">
       <c r="A52" s="43" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B52" s="44">
         <f>SUM(N52:Q52)</f>
@@ -5446,7 +5511,7 @@
     </row>
     <row r="53" ht="61.5" customHeight="1" s="29">
       <c r="A53" s="43" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B53" s="44">
         <f>SUM(N53:Q53)</f>
@@ -5542,7 +5607,7 @@
     </row>
     <row r="54" ht="61.5" customHeight="1" s="29">
       <c r="A54" s="43" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B54" s="44">
         <f>SUM(N54:Q54)</f>
@@ -5638,7 +5703,7 @@
     </row>
     <row r="55" ht="61.5" customHeight="1" s="29">
       <c r="A55" s="43" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B55" s="44">
         <f>SUM(N55:Q55)</f>
@@ -5734,7 +5799,7 @@
     </row>
     <row r="56" ht="61.5" customHeight="1" s="29">
       <c r="A56" s="43" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B56" s="44">
         <f>SUM(N56:Q56)</f>
@@ -5830,7 +5895,7 @@
     </row>
     <row r="57" ht="61.5" customHeight="1" s="29">
       <c r="A57" s="43" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B57" s="44">
         <f>SUM(N57:Q57)</f>
@@ -5926,7 +5991,7 @@
     </row>
     <row r="58" ht="61.5" customHeight="1" s="29">
       <c r="A58" s="43" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B58" s="44">
         <f>SUM(N58:Q58)</f>
@@ -6022,7 +6087,7 @@
     </row>
     <row r="59" ht="61.5" customHeight="1" s="29">
       <c r="A59" s="43" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B59" s="44">
         <f>SUM(N59:Q59)</f>
@@ -6118,7 +6183,7 @@
     </row>
     <row r="60" ht="61.5" customHeight="1" s="29">
       <c r="A60" s="43" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B60" s="44">
         <f>SUM(N60:Q60)</f>
@@ -6214,7 +6279,7 @@
     </row>
     <row r="61" ht="61.5" customHeight="1" s="29">
       <c r="A61" s="43" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B61" s="44">
         <f>SUM(N61:Q61)</f>
@@ -6310,7 +6375,7 @@
     </row>
     <row r="62" ht="61.5" customHeight="1" s="29">
       <c r="A62" s="43" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B62" s="44">
         <f>SUM(N62:Q62)</f>
@@ -6406,7 +6471,7 @@
     </row>
     <row r="63" ht="61.5" customHeight="1" s="29">
       <c r="A63" s="43" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B63" s="44">
         <f>SUM(N63:Q63)</f>
@@ -6502,7 +6567,7 @@
     </row>
     <row r="64" ht="61.5" customHeight="1" s="29">
       <c r="A64" s="45" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B64" s="46">
         <f>SUM(N64:Q64)</f>
@@ -6598,7 +6663,7 @@
     </row>
     <row r="65" ht="61.5" customHeight="1" s="29">
       <c r="A65" s="45" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B65" s="46">
         <f>SUM(N65:Q65)</f>
@@ -6694,7 +6759,7 @@
     </row>
     <row r="66" ht="61.5" customHeight="1" s="29">
       <c r="A66" s="45" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B66" s="46">
         <f>SUM(N66:Q66)</f>
@@ -6790,7 +6855,7 @@
     </row>
     <row r="67" ht="61.5" customHeight="1" s="29">
       <c r="A67" s="45" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B67" s="46">
         <f>SUM(N67:Q67)</f>
@@ -6886,7 +6951,7 @@
     </row>
     <row r="68" ht="61.5" customHeight="1" s="29">
       <c r="A68" s="45" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B68" s="46">
         <f>SUM(N68:Q68)</f>
@@ -6982,7 +7047,7 @@
     </row>
     <row r="69" ht="61.5" customHeight="1" s="29">
       <c r="A69" s="45" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B69" s="46">
         <f>SUM(N69:Q69)</f>
@@ -7078,7 +7143,7 @@
     </row>
     <row r="70" ht="61.5" customHeight="1" s="29">
       <c r="A70" s="45" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B70" s="46">
         <f>SUM(N70:Q70)</f>
@@ -7174,7 +7239,7 @@
     </row>
     <row r="71" ht="61.5" customHeight="1" s="29">
       <c r="A71" s="45" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B71" s="46">
         <f>SUM(N71:Q71)</f>
@@ -7270,7 +7335,7 @@
     </row>
     <row r="72" ht="61.5" customHeight="1" s="29">
       <c r="A72" s="45" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B72" s="46">
         <f>SUM(N72:Q72)</f>
@@ -7366,7 +7431,7 @@
     </row>
     <row r="73" ht="61.5" customHeight="1" s="29">
       <c r="A73" s="45" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B73" s="46">
         <f>SUM(N73:Q73)</f>
@@ -7462,7 +7527,7 @@
     </row>
     <row r="74" ht="61.5" customHeight="1" s="29">
       <c r="A74" s="45" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B74" s="46">
         <f>SUM(N74:Q74)</f>
@@ -7558,7 +7623,7 @@
     </row>
     <row r="75" ht="61.5" customHeight="1" s="29">
       <c r="A75" s="45" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B75" s="46">
         <f>SUM(N75:Q75)</f>
@@ -7650,7 +7715,7 @@
     </row>
     <row r="76" ht="61.5" customHeight="1" s="29">
       <c r="A76" s="45" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B76" s="46">
         <f>SUM(N76:Q76)</f>
@@ -7744,70 +7809,756 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="15" customHeight="1" s="29">
-      <c r="A78" s="47" t="inlineStr">
-        <is>
-          <t>Total des occasions</t>
-        </is>
-      </c>
-      <c r="B78" s="47">
-        <f>COUNTA(D5:D76)</f>
+    <row r="77" ht="62" customHeight="1" s="29">
+      <c r="A77" s="60" t="n">
+        <v>7</v>
+      </c>
+      <c r="B77" s="61">
+        <f>SUM(N77:Q77)</f>
         <v/>
       </c>
-    </row>
-    <row r="79" ht="15" customHeight="1" s="29">
-      <c r="A79" s="48" t="inlineStr">
-        <is>
-          <t>Priorité A</t>
-        </is>
-      </c>
-      <c r="B79" s="48">
-        <f>COUNTIF(C5:C76,"A")</f>
+      <c r="C77" s="61" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D77" s="62" t="inlineStr">
+        <is>
+          <t>Gourmet Sauvage</t>
+        </is>
+      </c>
+      <c r="E77" s="63" t="inlineStr">
+        <is>
+          <t>https://gourmetsauvage.ca/</t>
+        </is>
+      </c>
+      <c r="F77" s="64" t="inlineStr">
+        <is>
+          <t>Partenaire de filière, asclépiade comestible</t>
+        </is>
+      </c>
+      <c r="G77" s="64" t="inlineStr">
+        <is>
+          <t>Ajout du 3 août 2026</t>
+        </is>
+      </c>
+      <c r="H77" s="64" t="inlineStr">
+        <is>
+          <t>Entreprise des Laurentides, 30 ans de cueillette sauvage, fondée par Gérald Le Gal et reprise par Ariane Paré-Le Gal. Vend des gousses d'asclépiade marinées et donne des ateliers de cueillette.</t>
+        </is>
+      </c>
+      <c r="I77" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade + page mission</t>
+        </is>
+      </c>
+      <c r="J77" s="64" t="inlineStr">
+        <is>
+          <t>La complémentarité la plus nette de tout l'audit : ils utilisent la pousse, le bouton et la jeune gousse, Lasclay utilise la soie du follicule mûr. Aucune concurrence, la même plante, deux saisons différentes. Proposer un contenu croisé sur le cycle complet de la plante.</t>
+        </is>
+      </c>
+      <c r="K77" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L77" s="64" t="inlineStr">
+        <is>
+          <t>À trouver (formulaire de contact)</t>
+        </is>
+      </c>
+      <c r="M77" s="64" t="inlineStr">
+        <is>
+          <t>gourmetsauvage.ca/en/contact/ | Saint-Faustin-Lac-Carré, Laurentides</t>
+        </is>
+      </c>
+      <c r="N77" s="60" t="n">
+        <v>29</v>
+      </c>
+      <c r="O77" s="60" t="n">
+        <v>18</v>
+      </c>
+      <c r="P77" s="60" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q77" s="60" t="n">
+        <v>15</v>
+      </c>
+      <c r="R77" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S77" s="64" t="inlineStr">
+        <is>
+          <t>Angle éditorial fort : une seule plante, deux usages, zéro concurrence.</t>
+        </is>
+      </c>
+      <c r="T77" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U77" s="64" t="inlineStr">
+        <is>
+          <t>Occasion à qualifier puis à contacter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="62" customHeight="1" s="29">
+      <c r="A78" s="60" t="n">
+        <v>23</v>
+      </c>
+      <c r="B78" s="61">
+        <f>SUM(N78:Q78)</f>
         <v/>
       </c>
-    </row>
-    <row r="80" ht="15" customHeight="1" s="29">
-      <c r="A80" s="48" t="inlineStr">
-        <is>
-          <t>Priorité B</t>
-        </is>
-      </c>
-      <c r="B80" s="48">
-        <f>COUNTIF(C5:C76,"B")</f>
+      <c r="C78" s="61" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D78" s="62" t="inlineStr">
+        <is>
+          <t>Symbiose Herboristerie</t>
+        </is>
+      </c>
+      <c r="E78" s="63" t="inlineStr">
+        <is>
+          <t>https://www.symbioseherboristerie.com/blogue/lasclepiade-en-cuisine/</t>
+        </is>
+      </c>
+      <c r="F78" s="64" t="inlineStr">
+        <is>
+          <t>Mention existante, blogue</t>
+        </is>
+      </c>
+      <c r="G78" s="64" t="inlineStr">
+        <is>
+          <t>Ajout du 3 août 2026</t>
+        </is>
+      </c>
+      <c r="H78" s="64" t="inlineStr">
+        <is>
+          <t>Article « L'asclépiade en cuisine ».</t>
+        </is>
+      </c>
+      <c r="I78" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J78" s="64" t="inlineStr">
+        <is>
+          <t>Rien à demander, le lien est déjà là. Remercier et entretenir la relation.</t>
+        </is>
+      </c>
+      <c r="K78" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L78" s="64" t="inlineStr">
+        <is>
+          <t>À trouver (page de contact)</t>
+        </is>
+      </c>
+      <c r="M78" s="64" t="inlineStr">
+        <is>
+          <t>symbioseherboristerie.com/contact/</t>
+        </is>
+      </c>
+      <c r="N78" s="60" t="n">
+        <v>28</v>
+      </c>
+      <c r="O78" s="60" t="n">
+        <v>12</v>
+      </c>
+      <c r="P78" s="60" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q78" s="60" t="n">
+        <v>13</v>
+      </c>
+      <c r="R78" s="64" t="inlineStr">
+        <is>
+          <t>Lien obtenu</t>
+        </is>
+      </c>
+      <c r="S78" s="64" t="inlineStr">
+        <is>
+          <t>Découvert hors de l'audit initial. Te liait déjà sans que ce soit su.</t>
+        </is>
+      </c>
+      <c r="T78" s="65" t="inlineStr">
+        <is>
+          <t>OUI, lien en place (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U78" s="64" t="inlineStr">
+        <is>
+          <t>Rien à demander, le lien est déjà en place.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="62" customHeight="1" s="29">
+      <c r="A79" s="66" t="n">
+        <v>50</v>
+      </c>
+      <c r="B79" s="67">
+        <f>SUM(N79:Q79)</f>
         <v/>
       </c>
-    </row>
-    <row r="81" ht="15" customHeight="1" s="29">
-      <c r="A81" s="48" t="inlineStr">
-        <is>
-          <t>Priorité C</t>
-        </is>
-      </c>
-      <c r="B81" s="48">
-        <f>COUNTIF(C5:C76,"C")</f>
+      <c r="C79" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D79" s="62" t="inlineStr">
+        <is>
+          <t>Herbasimple</t>
+        </is>
+      </c>
+      <c r="E79" s="63" t="inlineStr">
+        <is>
+          <t>https://herbasimple.com/blog/asclepiade-commune-toxique-ou-comestible/</t>
+        </is>
+      </c>
+      <c r="F79" s="64" t="inlineStr">
+        <is>
+          <t>Page ressource, asclépiade</t>
+        </is>
+      </c>
+      <c r="G79" s="64" t="inlineStr">
+        <is>
+          <t>Ajout du 3 août 2026</t>
+        </is>
+      </c>
+      <c r="H79" s="64" t="inlineStr">
+        <is>
+          <t>Article « Asclépiade commune : toxique ou comestible ? ».</t>
+        </is>
+      </c>
+      <c r="I79" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J79" s="64" t="inlineStr">
+        <is>
+          <t>Sujet voisin, public curieux de la plante. Proposer la page pilier en complément botanique.</t>
+        </is>
+      </c>
+      <c r="K79" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L79" s="64" t="inlineStr">
+        <is>
+          <t>À trouver (page de contact)</t>
+        </is>
+      </c>
+      <c r="M79" s="64" t="inlineStr">
+        <is>
+          <t>herbasimple.com</t>
+        </is>
+      </c>
+      <c r="N79" s="66" t="n">
+        <v>26</v>
+      </c>
+      <c r="O79" s="66" t="n">
+        <v>12</v>
+      </c>
+      <c r="P79" s="66" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q79" s="66" t="n">
+        <v>11</v>
+      </c>
+      <c r="R79" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S79" s="64" t="inlineStr"/>
+      <c r="T79" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U79" s="64" t="inlineStr">
+        <is>
+          <t>Occasion à qualifier puis à contacter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="62" customHeight="1" s="29">
+      <c r="A80" s="66" t="n">
+        <v>53</v>
+      </c>
+      <c r="B80" s="67">
+        <f>SUM(N80:Q80)</f>
         <v/>
       </c>
-    </row>
-    <row r="82" ht="15" customHeight="1" s="29">
-      <c r="A82" s="48" t="inlineStr">
-        <is>
-          <t>Courriels confirmés</t>
-        </is>
-      </c>
-      <c r="B82" s="48">
-        <f>COUNTIF(L5:L76,"Confirmé*")</f>
+      <c r="C80" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D80" s="62" t="inlineStr">
+        <is>
+          <t>Banlieusardises</t>
+        </is>
+      </c>
+      <c r="E80" s="63" t="inlineStr">
+        <is>
+          <t>https://www.banlieusardises.com/gousses-dasclepiades-sautees-au-beurre/</t>
+        </is>
+      </c>
+      <c r="F80" s="64" t="inlineStr">
+        <is>
+          <t>Page ressource, recette</t>
+        </is>
+      </c>
+      <c r="G80" s="64" t="inlineStr">
+        <is>
+          <t>Ajout du 3 août 2026</t>
+        </is>
+      </c>
+      <c r="H80" s="64" t="inlineStr">
+        <is>
+          <t>Recette de gousses d'asclépiades sautées au beurre sur un blogue québécois de longue date.</t>
+        </is>
+      </c>
+      <c r="I80" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J80" s="64" t="inlineStr">
+        <is>
+          <t>Blogue personnel établi, facile à joindre. Offrir la ressource botanique en complément de la recette.</t>
+        </is>
+      </c>
+      <c r="K80" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L80" s="64" t="inlineStr">
+        <is>
+          <t>À trouver (page de contact)</t>
+        </is>
+      </c>
+      <c r="M80" s="64" t="inlineStr">
+        <is>
+          <t>banlieusardises.com</t>
+        </is>
+      </c>
+      <c r="N80" s="66" t="n">
+        <v>24</v>
+      </c>
+      <c r="O80" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="P80" s="66" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q80" s="66" t="n">
+        <v>10</v>
+      </c>
+      <c r="R80" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S80" s="64" t="inlineStr"/>
+      <c r="T80" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U80" s="64" t="inlineStr">
+        <is>
+          <t>Occasion à qualifier puis à contacter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="62" customHeight="1" s="29">
+      <c r="A81" s="66" t="n">
+        <v>45</v>
+      </c>
+      <c r="B81" s="67">
+        <f>SUM(N81:Q81)</f>
         <v/>
       </c>
-    </row>
-    <row r="83" ht="15" customHeight="1" s="29">
-      <c r="A83" s="47" t="inlineStr">
-        <is>
-          <t>Liens obtenus</t>
-        </is>
-      </c>
-      <c r="B83" s="47">
-        <f>COUNTIF(R5:R76,"Lien obtenu")</f>
+      <c r="C81" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D81" s="62" t="inlineStr">
+        <is>
+          <t>La Presse (asclépiade comestible, 2014)</t>
+        </is>
+      </c>
+      <c r="E81" s="63" t="inlineStr">
+        <is>
+          <t>https://www.lapresse.ca/vivre/gourmand/cuisine/terroir/201407/31/01-4788196-decouvrir-lasclepiade-commune.php</t>
+        </is>
+      </c>
+      <c r="F81" s="64" t="inlineStr">
+        <is>
+          <t>Presse nationale, sujet asclépiade</t>
+        </is>
+      </c>
+      <c r="G81" s="64" t="inlineStr">
+        <is>
+          <t>Ajout du 3 août 2026</t>
+        </is>
+      </c>
+      <c r="H81" s="64" t="inlineStr">
+        <is>
+          <t>Article « Découvrir l'asclépiade commune » dans la section terroir.</t>
+        </is>
+      </c>
+      <c r="I81" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J81" s="64" t="inlineStr">
+        <is>
+          <t>Article ancien. Se rendre disponible comme source pour une reprise du sujet.</t>
+        </is>
+      </c>
+      <c r="K81" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L81" s="64" t="inlineStr">
+        <is>
+          <t>À trouver (contacter la ou le signataire)</t>
+        </is>
+      </c>
+      <c r="M81" s="64" t="inlineStr"/>
+      <c r="N81" s="66" t="n">
+        <v>24</v>
+      </c>
+      <c r="O81" s="66" t="n">
+        <v>25</v>
+      </c>
+      <c r="P81" s="66" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q81" s="66" t="n">
+        <v>12</v>
+      </c>
+      <c r="R81" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S81" s="64" t="inlineStr">
+        <is>
+          <t>Angle alimentaire, pas textile. Public différent mais même plante.</t>
+        </is>
+      </c>
+      <c r="T81" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U81" s="64" t="inlineStr">
+        <is>
+          <t>Occasion à qualifier puis à contacter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="62" customHeight="1" s="29">
+      <c r="A82" s="66" t="n">
+        <v>46</v>
+      </c>
+      <c r="B82" s="67">
+        <f>SUM(N82:Q82)</f>
         <v/>
+      </c>
+      <c r="C82" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D82" s="62" t="inlineStr">
+        <is>
+          <t>Lufa (blogue)</t>
+        </is>
+      </c>
+      <c r="E82" s="63" t="inlineStr">
+        <is>
+          <t>https://montreal.lufa.com/fr/blog/recettes/apprivoiser-les-aliments-sauvages-tresors-et-recettes-de-gourmet-sauvage</t>
+        </is>
+      </c>
+      <c r="F82" s="64" t="inlineStr">
+        <is>
+          <t>Blogue de marque, aliments sauvages</t>
+        </is>
+      </c>
+      <c r="G82" s="64" t="inlineStr">
+        <is>
+          <t>Ajout du 3 août 2026</t>
+        </is>
+      </c>
+      <c r="H82" s="64" t="inlineStr">
+        <is>
+          <t>Billet sur les aliments sauvages avec Gourmet Sauvage. Grande plateforme d'agriculture urbaine à Montréal.</t>
+        </is>
+      </c>
+      <c r="I82" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade + collection semences</t>
+        </is>
+      </c>
+      <c r="J82" s="64" t="inlineStr">
+        <is>
+          <t>Angle partenariat plutôt que lien : ils ont un programme de partenaires et des points de chute.</t>
+        </is>
+      </c>
+      <c r="K82" s="64" t="inlineStr">
+        <is>
+          <t>partenaires@lufa.com</t>
+        </is>
+      </c>
+      <c r="L82" s="64" t="inlineStr">
+        <is>
+          <t>Confirmé</t>
+        </is>
+      </c>
+      <c r="M82" s="64" t="inlineStr">
+        <is>
+          <t>pointsdechute@lufa.com</t>
+        </is>
+      </c>
+      <c r="N82" s="66" t="n">
+        <v>20</v>
+      </c>
+      <c r="O82" s="66" t="n">
+        <v>20</v>
+      </c>
+      <c r="P82" s="66" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q82" s="66" t="n">
+        <v>14</v>
+      </c>
+      <c r="R82" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S82" s="64" t="inlineStr">
+        <is>
+          <t>Piste commerciale autant que piste de lien.</t>
+        </is>
+      </c>
+      <c r="T82" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U82" s="64" t="inlineStr">
+        <is>
+          <t>Occasion à qualifier puis à contacter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="62" customHeight="1" s="29">
+      <c r="A83" s="68" t="n">
+        <v>73</v>
+      </c>
+      <c r="B83" s="69">
+        <f>SUM(N83:Q83)</f>
+        <v/>
+      </c>
+      <c r="C83" s="69" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D83" s="62" t="inlineStr">
+        <is>
+          <t>Journal Le Tour</t>
+        </is>
+      </c>
+      <c r="E83" s="63" t="inlineStr">
+        <is>
+          <t>https://journalletour.com/plantes-sauvages-comestibles/</t>
+        </is>
+      </c>
+      <c r="F83" s="64" t="inlineStr">
+        <is>
+          <t>Média local, plantes sauvages</t>
+        </is>
+      </c>
+      <c r="G83" s="64" t="inlineStr">
+        <is>
+          <t>Ajout du 3 août 2026</t>
+        </is>
+      </c>
+      <c r="H83" s="64" t="inlineStr">
+        <is>
+          <t>Article sur les plantes sauvages comestibles du printemps.</t>
+        </is>
+      </c>
+      <c r="I83" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J83" s="64" t="inlineStr">
+        <is>
+          <t>Petit média accessible. Offrir un contenu sur l'asclépiade au-delà de l'assiette.</t>
+        </is>
+      </c>
+      <c r="K83" s="64" t="inlineStr">
+        <is>
+          <t>annieaire@gmail.com</t>
+        </is>
+      </c>
+      <c r="L83" s="64" t="inlineStr">
+        <is>
+          <t>Confirmé (trouvé sur la page)</t>
+        </is>
+      </c>
+      <c r="M83" s="64" t="inlineStr">
+        <is>
+          <t>journalletour.com</t>
+        </is>
+      </c>
+      <c r="N83" s="68" t="n">
+        <v>20</v>
+      </c>
+      <c r="O83" s="68" t="n">
+        <v>9</v>
+      </c>
+      <c r="P83" s="68" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q83" s="68" t="n">
+        <v>8</v>
+      </c>
+      <c r="R83" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S83" s="64" t="inlineStr"/>
+      <c r="T83" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U83" s="64" t="inlineStr">
+        <is>
+          <t>Occasion à qualifier puis à contacter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="62" customHeight="1" s="29">
+      <c r="A84" s="66" t="n">
+        <v>30</v>
+      </c>
+      <c r="B84" s="67">
+        <f>SUM(N84:Q84)</f>
+        <v/>
+      </c>
+      <c r="C84" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D84" s="62" t="inlineStr">
+        <is>
+          <t>Unpointcinq</t>
+        </is>
+      </c>
+      <c r="E84" s="63" t="inlineStr">
+        <is>
+          <t>https://unpointcinq.ca/agir/plantes-sauvages-comestibles-quebec/</t>
+        </is>
+      </c>
+      <c r="F84" s="64" t="inlineStr">
+        <is>
+          <t>Média climat, plantes sauvages</t>
+        </is>
+      </c>
+      <c r="G84" s="64" t="inlineStr">
+        <is>
+          <t>Ajout du 3 août 2026</t>
+        </is>
+      </c>
+      <c r="H84" s="64" t="inlineStr">
+        <is>
+          <t>Article « Savez-vous manger les plantes, à la mode de chez nous ? ». Média québécois consacré à l'action climatique.</t>
+        </is>
+      </c>
+      <c r="I84" s="64" t="inlineStr">
+        <is>
+          <t>Page mission + page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J84" s="64" t="inlineStr">
+        <is>
+          <t>Média dont la ligne éditoriale colle exactement à la mission de Lasclay. Proposer un sujet sur la culture de l'asclépiade comme levier d'habitat.</t>
+        </is>
+      </c>
+      <c r="K84" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L84" s="64" t="inlineStr">
+        <is>
+          <t>À trouver (rédaction)</t>
+        </is>
+      </c>
+      <c r="M84" s="64" t="inlineStr">
+        <is>
+          <t>unpointcinq.ca</t>
+        </is>
+      </c>
+      <c r="N84" s="66" t="n">
+        <v>26</v>
+      </c>
+      <c r="O84" s="66" t="n">
+        <v>19</v>
+      </c>
+      <c r="P84" s="66" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q84" s="66" t="n">
+        <v>14</v>
+      </c>
+      <c r="R84" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S84" s="64" t="inlineStr">
+        <is>
+          <t>Un des meilleurs alignements éditoriaux du lot.</t>
+        </is>
+      </c>
+      <c r="T84" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U84" s="64" t="inlineStr">
+        <is>
+          <t>Occasion à qualifier puis à contacter.</t>
+        </is>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="29">
@@ -7866,7 +8617,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:U76"/>
+  <autoFilter ref="A4:U84"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A1:S1"/>
@@ -7953,6 +8704,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" display="https://www.madetomeasuremag.com/vegeto-launches-sustainable-heavy-duty-insulation-material-made-of-milkweed" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" display="https://lemarcheauxtresors.company.site/" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" display="https://www.lhebdodustmaurice.com/actualites/nouveau-partenaire-developpement-de-lasclepiade/" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId80"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/seo/backlinks-lasclay-audit.xlsx
+++ b/seo/backlinks-lasclay-audit.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Pistes à vérifier" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunités'!$A$4:$U$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Opportunités'!$A$4:$U$144</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Pistes à vérifier'!$A$4:$H$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -150,6 +150,18 @@
       <sz val="10"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F4E3D"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F4E3D"/>
+      <sz val="12"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -261,7 +273,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -469,6 +481,21 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -780,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:U89"/>
+  <dimension ref="A1:U144"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="28" min="1" max="1"/>
@@ -814,7 +841,7 @@
     <row r="2" ht="15" customHeight="1" s="29">
       <c r="A2" s="31" t="inlineStr">
         <is>
-          <t>Références à Lasclay ou à l'asclépiade repérées sur le web, classées par qualité d'occasion. Vérification des liens effectuée le 3 août 2026 : 10 pages portent déjà un lien, 8 mentionnent Lasclay sans lien (les vraies occasions), 43 ne le mentionnent pas, 11 restent à ouvrir à la main. Voir la colonne « Lien en place ? ».</t>
+          <t>Audit exhaustif des références à Lasclay et à l'asclépiade sur le web, vérifiées une à une le 3 août 2026. 140 occasions. 11 pages portent déjà un lien vers lasclay.com. 10 mentionnent Lasclay sans lien : ce sont les occasions les plus mûres. 22 pages refusent les requêtes automatisées et restent à ouvrir à la main. 35 courriels sont confirmés.</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1818,7 @@
     </row>
     <row r="14" ht="61.5" customHeight="1" s="29">
       <c r="A14" s="33" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B14" s="34">
         <f>SUM(N14:Q14)</f>
@@ -1883,7 +1910,7 @@
     </row>
     <row r="15" ht="61.5" customHeight="1" s="29">
       <c r="A15" s="33" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B15" s="34">
         <f>SUM(N15:Q15)</f>
@@ -1979,7 +2006,7 @@
     </row>
     <row r="16" ht="61.5" customHeight="1" s="29">
       <c r="A16" s="33" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B16" s="34">
         <f>SUM(N16:Q16)</f>
@@ -2075,7 +2102,7 @@
     </row>
     <row r="17" ht="61.5" customHeight="1" s="29">
       <c r="A17" s="33" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B17" s="34">
         <f>SUM(N17:Q17)</f>
@@ -2171,7 +2198,7 @@
     </row>
     <row r="18" ht="61.5" customHeight="1" s="29">
       <c r="A18" s="33" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B18" s="34">
         <f>SUM(N18:Q18)</f>
@@ -2263,7 +2290,7 @@
     </row>
     <row r="19" ht="61.5" customHeight="1" s="29">
       <c r="A19" s="33" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B19" s="34">
         <f>SUM(N19:Q19)</f>
@@ -2359,7 +2386,7 @@
     </row>
     <row r="20" ht="61.5" customHeight="1" s="29">
       <c r="A20" s="33" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B20" s="34">
         <f>SUM(N20:Q20)</f>
@@ -2455,7 +2482,7 @@
     </row>
     <row r="21" ht="61.5" customHeight="1" s="29">
       <c r="A21" s="33" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B21" s="34">
         <f>SUM(N21:Q21)</f>
@@ -2551,7 +2578,7 @@
     </row>
     <row r="22" ht="61.5" customHeight="1" s="29">
       <c r="A22" s="33" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B22" s="34">
         <f>SUM(N22:Q22)</f>
@@ -2647,7 +2674,7 @@
     </row>
     <row r="23" ht="61.5" customHeight="1" s="29">
       <c r="A23" s="33" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B23" s="34">
         <f>SUM(N23:Q23)</f>
@@ -2743,7 +2770,7 @@
     </row>
     <row r="24" ht="61.5" customHeight="1" s="29">
       <c r="A24" s="33" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B24" s="34">
         <f>SUM(N24:Q24)</f>
@@ -2839,7 +2866,7 @@
     </row>
     <row r="25" ht="61.5" customHeight="1" s="29">
       <c r="A25" s="33" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B25" s="34">
         <f>SUM(N25:Q25)</f>
@@ -2935,7 +2962,7 @@
     </row>
     <row r="26" ht="61.5" customHeight="1" s="29">
       <c r="A26" s="43" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B26" s="44">
         <f>SUM(N26:Q26)</f>
@@ -3031,7 +3058,7 @@
     </row>
     <row r="27" ht="61.5" customHeight="1" s="29">
       <c r="A27" s="43" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B27" s="44">
         <f>SUM(N27:Q27)</f>
@@ -3127,7 +3154,7 @@
     </row>
     <row r="28" ht="61.5" customHeight="1" s="29">
       <c r="A28" s="43" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B28" s="44">
         <f>SUM(N28:Q28)</f>
@@ -3219,7 +3246,7 @@
     </row>
     <row r="29" ht="61.5" customHeight="1" s="29">
       <c r="A29" s="43" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B29" s="44">
         <f>SUM(N29:Q29)</f>
@@ -3311,7 +3338,7 @@
     </row>
     <row r="30" ht="61.5" customHeight="1" s="29">
       <c r="A30" s="43" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B30" s="44">
         <f>SUM(N30:Q30)</f>
@@ -3407,7 +3434,7 @@
     </row>
     <row r="31" ht="61.5" customHeight="1" s="29">
       <c r="A31" s="43" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B31" s="44">
         <f>SUM(N31:Q31)</f>
@@ -3503,7 +3530,7 @@
     </row>
     <row r="32" ht="61.5" customHeight="1" s="29">
       <c r="A32" s="43" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B32" s="44">
         <f>SUM(N32:Q32)</f>
@@ -3595,7 +3622,7 @@
     </row>
     <row r="33" ht="61.5" customHeight="1" s="29">
       <c r="A33" s="43" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B33" s="44">
         <f>SUM(N33:Q33)</f>
@@ -3691,7 +3718,7 @@
     </row>
     <row r="34" ht="61.5" customHeight="1" s="29">
       <c r="A34" s="43" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B34" s="44">
         <f>SUM(N34:Q34)</f>
@@ -3787,7 +3814,7 @@
     </row>
     <row r="35" ht="61.5" customHeight="1" s="29">
       <c r="A35" s="43" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B35" s="44">
         <f>SUM(N35:Q35)</f>
@@ -3883,7 +3910,7 @@
     </row>
     <row r="36" ht="61.5" customHeight="1" s="29">
       <c r="A36" s="43" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B36" s="44">
         <f>SUM(N36:Q36)</f>
@@ -3975,7 +4002,7 @@
     </row>
     <row r="37" ht="61.5" customHeight="1" s="29">
       <c r="A37" s="43" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B37" s="44">
         <f>SUM(N37:Q37)</f>
@@ -4071,7 +4098,7 @@
     </row>
     <row r="38" ht="61.5" customHeight="1" s="29">
       <c r="A38" s="43" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B38" s="44">
         <f>SUM(N38:Q38)</f>
@@ -4167,7 +4194,7 @@
     </row>
     <row r="39" ht="61.5" customHeight="1" s="29">
       <c r="A39" s="43" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B39" s="44">
         <f>SUM(N39:Q39)</f>
@@ -4263,7 +4290,7 @@
     </row>
     <row r="40" ht="61.5" customHeight="1" s="29">
       <c r="A40" s="43" t="n">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="B40" s="44">
         <f>SUM(N40:Q40)</f>
@@ -4359,7 +4386,7 @@
     </row>
     <row r="41" ht="61.5" customHeight="1" s="29">
       <c r="A41" s="43" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="B41" s="44">
         <f>SUM(N41:Q41)</f>
@@ -4455,7 +4482,7 @@
     </row>
     <row r="42" ht="61.5" customHeight="1" s="29">
       <c r="A42" s="43" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="B42" s="44">
         <f>SUM(N42:Q42)</f>
@@ -4551,7 +4578,7 @@
     </row>
     <row r="43" ht="61.5" customHeight="1" s="29">
       <c r="A43" s="43" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="B43" s="44">
         <f>SUM(N43:Q43)</f>
@@ -4647,7 +4674,7 @@
     </row>
     <row r="44" ht="61.5" customHeight="1" s="29">
       <c r="A44" s="43" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="B44" s="44">
         <f>SUM(N44:Q44)</f>
@@ -4743,7 +4770,7 @@
     </row>
     <row r="45" ht="61.5" customHeight="1" s="29">
       <c r="A45" s="43" t="n">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="B45" s="44">
         <f>SUM(N45:Q45)</f>
@@ -4839,7 +4866,7 @@
     </row>
     <row r="46" ht="61.5" customHeight="1" s="29">
       <c r="A46" s="43" t="n">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="B46" s="44">
         <f>SUM(N46:Q46)</f>
@@ -4935,7 +4962,7 @@
     </row>
     <row r="47" ht="61.5" customHeight="1" s="29">
       <c r="A47" s="43" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="B47" s="44">
         <f>SUM(N47:Q47)</f>
@@ -5031,7 +5058,7 @@
     </row>
     <row r="48" ht="61.5" customHeight="1" s="29">
       <c r="A48" s="43" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="B48" s="44">
         <f>SUM(N48:Q48)</f>
@@ -5127,7 +5154,7 @@
     </row>
     <row r="49" ht="61.5" customHeight="1" s="29">
       <c r="A49" s="43" t="n">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="B49" s="44">
         <f>SUM(N49:Q49)</f>
@@ -5223,7 +5250,7 @@
     </row>
     <row r="50" ht="61.5" customHeight="1" s="29">
       <c r="A50" s="43" t="n">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="B50" s="44">
         <f>SUM(N50:Q50)</f>
@@ -5319,7 +5346,7 @@
     </row>
     <row r="51" ht="61.5" customHeight="1" s="29">
       <c r="A51" s="43" t="n">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="B51" s="44">
         <f>SUM(N51:Q51)</f>
@@ -5415,7 +5442,7 @@
     </row>
     <row r="52" ht="61.5" customHeight="1" s="29">
       <c r="A52" s="43" t="n">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="B52" s="44">
         <f>SUM(N52:Q52)</f>
@@ -5511,7 +5538,7 @@
     </row>
     <row r="53" ht="61.5" customHeight="1" s="29">
       <c r="A53" s="43" t="n">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="B53" s="44">
         <f>SUM(N53:Q53)</f>
@@ -5607,7 +5634,7 @@
     </row>
     <row r="54" ht="61.5" customHeight="1" s="29">
       <c r="A54" s="43" t="n">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="B54" s="44">
         <f>SUM(N54:Q54)</f>
@@ -5703,7 +5730,7 @@
     </row>
     <row r="55" ht="61.5" customHeight="1" s="29">
       <c r="A55" s="43" t="n">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="B55" s="44">
         <f>SUM(N55:Q55)</f>
@@ -5799,7 +5826,7 @@
     </row>
     <row r="56" ht="61.5" customHeight="1" s="29">
       <c r="A56" s="43" t="n">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="B56" s="44">
         <f>SUM(N56:Q56)</f>
@@ -5895,7 +5922,7 @@
     </row>
     <row r="57" ht="61.5" customHeight="1" s="29">
       <c r="A57" s="43" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="B57" s="44">
         <f>SUM(N57:Q57)</f>
@@ -5991,7 +6018,7 @@
     </row>
     <row r="58" ht="61.5" customHeight="1" s="29">
       <c r="A58" s="43" t="n">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="B58" s="44">
         <f>SUM(N58:Q58)</f>
@@ -6087,7 +6114,7 @@
     </row>
     <row r="59" ht="61.5" customHeight="1" s="29">
       <c r="A59" s="43" t="n">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="B59" s="44">
         <f>SUM(N59:Q59)</f>
@@ -6183,7 +6210,7 @@
     </row>
     <row r="60" ht="61.5" customHeight="1" s="29">
       <c r="A60" s="43" t="n">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="B60" s="44">
         <f>SUM(N60:Q60)</f>
@@ -6279,7 +6306,7 @@
     </row>
     <row r="61" ht="61.5" customHeight="1" s="29">
       <c r="A61" s="43" t="n">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="B61" s="44">
         <f>SUM(N61:Q61)</f>
@@ -6375,7 +6402,7 @@
     </row>
     <row r="62" ht="61.5" customHeight="1" s="29">
       <c r="A62" s="43" t="n">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="B62" s="44">
         <f>SUM(N62:Q62)</f>
@@ -6471,7 +6498,7 @@
     </row>
     <row r="63" ht="61.5" customHeight="1" s="29">
       <c r="A63" s="43" t="n">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="B63" s="44">
         <f>SUM(N63:Q63)</f>
@@ -6567,7 +6594,7 @@
     </row>
     <row r="64" ht="61.5" customHeight="1" s="29">
       <c r="A64" s="45" t="n">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="B64" s="46">
         <f>SUM(N64:Q64)</f>
@@ -6663,7 +6690,7 @@
     </row>
     <row r="65" ht="61.5" customHeight="1" s="29">
       <c r="A65" s="45" t="n">
-        <v>68</v>
+        <v>121</v>
       </c>
       <c r="B65" s="46">
         <f>SUM(N65:Q65)</f>
@@ -6759,7 +6786,7 @@
     </row>
     <row r="66" ht="61.5" customHeight="1" s="29">
       <c r="A66" s="45" t="n">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="B66" s="46">
         <f>SUM(N66:Q66)</f>
@@ -6855,7 +6882,7 @@
     </row>
     <row r="67" ht="61.5" customHeight="1" s="29">
       <c r="A67" s="45" t="n">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="B67" s="46">
         <f>SUM(N67:Q67)</f>
@@ -6951,7 +6978,7 @@
     </row>
     <row r="68" ht="61.5" customHeight="1" s="29">
       <c r="A68" s="45" t="n">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="B68" s="46">
         <f>SUM(N68:Q68)</f>
@@ -7047,7 +7074,7 @@
     </row>
     <row r="69" ht="61.5" customHeight="1" s="29">
       <c r="A69" s="45" t="n">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="B69" s="46">
         <f>SUM(N69:Q69)</f>
@@ -7143,7 +7170,7 @@
     </row>
     <row r="70" ht="61.5" customHeight="1" s="29">
       <c r="A70" s="45" t="n">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="B70" s="46">
         <f>SUM(N70:Q70)</f>
@@ -7239,7 +7266,7 @@
     </row>
     <row r="71" ht="61.5" customHeight="1" s="29">
       <c r="A71" s="45" t="n">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="B71" s="46">
         <f>SUM(N71:Q71)</f>
@@ -7335,7 +7362,7 @@
     </row>
     <row r="72" ht="61.5" customHeight="1" s="29">
       <c r="A72" s="45" t="n">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="B72" s="46">
         <f>SUM(N72:Q72)</f>
@@ -7431,7 +7458,7 @@
     </row>
     <row r="73" ht="61.5" customHeight="1" s="29">
       <c r="A73" s="45" t="n">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="B73" s="46">
         <f>SUM(N73:Q73)</f>
@@ -7527,7 +7554,7 @@
     </row>
     <row r="74" ht="61.5" customHeight="1" s="29">
       <c r="A74" s="45" t="n">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="B74" s="46">
         <f>SUM(N74:Q74)</f>
@@ -7623,7 +7650,7 @@
     </row>
     <row r="75" ht="61.5" customHeight="1" s="29">
       <c r="A75" s="45" t="n">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="B75" s="46">
         <f>SUM(N75:Q75)</f>
@@ -7715,7 +7742,7 @@
     </row>
     <row r="76" ht="61.5" customHeight="1" s="29">
       <c r="A76" s="45" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="B76" s="46">
         <f>SUM(N76:Q76)</f>
@@ -7907,7 +7934,7 @@
     </row>
     <row r="78" ht="62" customHeight="1" s="29">
       <c r="A78" s="60" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B78" s="61">
         <f>SUM(N78:Q78)</f>
@@ -8003,7 +8030,7 @@
     </row>
     <row r="79" ht="62" customHeight="1" s="29">
       <c r="A79" s="66" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="B79" s="67">
         <f>SUM(N79:Q79)</f>
@@ -8095,7 +8122,7 @@
     </row>
     <row r="80" ht="62" customHeight="1" s="29">
       <c r="A80" s="66" t="n">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="B80" s="67">
         <f>SUM(N80:Q80)</f>
@@ -8187,7 +8214,7 @@
     </row>
     <row r="81" ht="62" customHeight="1" s="29">
       <c r="A81" s="66" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="B81" s="67">
         <f>SUM(N81:Q81)</f>
@@ -8279,7 +8306,7 @@
     </row>
     <row r="82" ht="62" customHeight="1" s="29">
       <c r="A82" s="66" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="B82" s="67">
         <f>SUM(N82:Q82)</f>
@@ -8375,7 +8402,7 @@
     </row>
     <row r="83" ht="62" customHeight="1" s="29">
       <c r="A83" s="68" t="n">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="B83" s="69">
         <f>SUM(N83:Q83)</f>
@@ -8467,7 +8494,7 @@
     </row>
     <row r="84" ht="62" customHeight="1" s="29">
       <c r="A84" s="66" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B84" s="67">
         <f>SUM(N84:Q84)</f>
@@ -8561,74 +8588,5550 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="15" customHeight="1" s="29">
-      <c r="A85" s="48" t="inlineStr">
-        <is>
-          <t>Vague 1, prêts à envoyer</t>
-        </is>
-      </c>
-      <c r="B85" s="48">
-        <f>COUNTIF(R5:R76,"Vague 1, prêt à envoyer")</f>
+    <row r="85" ht="62" customHeight="1" s="29">
+      <c r="A85" s="66" t="n">
+        <v>40</v>
+      </c>
+      <c r="B85" s="67">
+        <f>SUM(N85:Q85)</f>
         <v/>
       </c>
-    </row>
-    <row r="86" ht="15" customHeight="1" s="29">
-      <c r="A86" s="48" t="inlineStr">
-        <is>
-          <t>Vague 1, en attente du guide</t>
-        </is>
-      </c>
-      <c r="B86" s="48">
-        <f>COUNTIF(R5:R76,"Vague 1, en attente du guide")</f>
+      <c r="C85" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D85" s="62" t="inlineStr">
+        <is>
+          <t>Innofibre (CCTT, Trois-Rivières)</t>
+        </is>
+      </c>
+      <c r="E85" s="63" t="inlineStr">
+        <is>
+          <t>https://innofibre.ca/4548-2/</t>
+        </is>
+      </c>
+      <c r="F85" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, recherche</t>
+        </is>
+      </c>
+      <c r="G85" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H85" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « recherche ».</t>
+        </is>
+      </c>
+      <c r="I85" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J85" s="64" t="inlineStr">
+        <is>
+          <t>Centre de recherche sur la même fibre. Proposer une collaboration ou une étude de cas, le lien suit.</t>
+        </is>
+      </c>
+      <c r="K85" s="64" t="inlineStr">
+        <is>
+          <t>innofibre@cegeptr.qc.ca</t>
+        </is>
+      </c>
+      <c r="L85" s="64" t="inlineStr">
+        <is>
+          <t>Confirmé (trouvé sur la page)</t>
+        </is>
+      </c>
+      <c r="M85" s="64" t="inlineStr"/>
+      <c r="N85" s="66" t="n">
+        <v>26</v>
+      </c>
+      <c r="O85" s="66" t="n">
+        <v>22</v>
+      </c>
+      <c r="P85" s="66" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q85" s="66" t="n">
+        <v>12</v>
+      </c>
+      <c r="R85" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S85" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T85" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U85" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="62" customHeight="1" s="29">
+      <c r="A86" s="66" t="n">
+        <v>41</v>
+      </c>
+      <c r="B86" s="67">
+        <f>SUM(N86:Q86)</f>
         <v/>
       </c>
-    </row>
-    <row r="87" ht="15" customHeight="1" s="29">
-      <c r="A87" s="48" t="inlineStr">
-        <is>
-          <t>Bloqués par le guide</t>
-        </is>
-      </c>
-      <c r="B87" s="48">
-        <f>COUNTIF(R5:R76,"Bloqué : guide requis*")</f>
+      <c r="C86" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D86" s="62" t="inlineStr">
+        <is>
+          <t>ÉMA, Université de Sherbrooke</t>
+        </is>
+      </c>
+      <c r="E86" s="63" t="inlineStr">
+        <is>
+          <t>http://ema.recherche.usherbrooke.ca/?p=629</t>
+        </is>
+      </c>
+      <c r="F86" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, recherche</t>
+        </is>
+      </c>
+      <c r="G86" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H86" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « recherche ».</t>
+        </is>
+      </c>
+      <c r="I86" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J86" s="64" t="inlineStr">
+        <is>
+          <t>Centre de recherche sur la même fibre. Proposer une collaboration ou une étude de cas, le lien suit.</t>
+        </is>
+      </c>
+      <c r="K86" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L86" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M86" s="64" t="inlineStr"/>
+      <c r="N86" s="66" t="n">
+        <v>26</v>
+      </c>
+      <c r="O86" s="66" t="n">
+        <v>22</v>
+      </c>
+      <c r="P86" s="66" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q86" s="66" t="n">
+        <v>12</v>
+      </c>
+      <c r="R86" s="64" t="inlineStr">
+        <is>
+          <t>À qualifier</t>
+        </is>
+      </c>
+      <c r="S86" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T86" s="70" t="inlineStr">
+        <is>
+          <t>À ouvrir à la main</t>
+        </is>
+      </c>
+      <c r="U86" s="64" t="inlineStr">
+        <is>
+          <t>Le serveur refuse les requêtes automatisées. À ouvrir à la main (HTTP 403)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="62" customHeight="1" s="29">
+      <c r="A87" s="66" t="n">
+        <v>58</v>
+      </c>
+      <c r="B87" s="67">
+        <f>SUM(N87:Q87)</f>
         <v/>
       </c>
-    </row>
-    <row r="88" ht="15" customHeight="1" s="29">
-      <c r="A88" s="48" t="inlineStr">
-        <is>
-          <t>Bloqués par une adresse manquante</t>
-        </is>
-      </c>
-      <c r="B88" s="48">
-        <f>COUNTIF(R5:R76,"*courriel à trouver")</f>
+      <c r="C87" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D87" s="62" t="inlineStr">
+        <is>
+          <t>Magazine FORMES</t>
+        </is>
+      </c>
+      <c r="E87" s="63" t="inlineStr">
+        <is>
+          <t>https://www.formes.ca/materiaux/articles/fibre-d-asclepiade-des-revetements-durables-fabriques-au-quebec</t>
+        </is>
+      </c>
+      <c r="F87" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, presse spec</t>
+        </is>
+      </c>
+      <c r="G87" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H87" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « presse spec ».</t>
+        </is>
+      </c>
+      <c r="I87" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J87" s="64" t="inlineStr">
+        <is>
+          <t>Presse spécialisée. Envoyer une nouvelle factuelle plutôt qu'une demande de lien.</t>
+        </is>
+      </c>
+      <c r="K87" s="64" t="inlineStr">
+        <is>
+          <t>info@formes.ca</t>
+        </is>
+      </c>
+      <c r="L87" s="64" t="inlineStr">
+        <is>
+          <t>Confirmé (trouvé sur la page)</t>
+        </is>
+      </c>
+      <c r="M87" s="64" t="inlineStr"/>
+      <c r="N87" s="66" t="n">
+        <v>26</v>
+      </c>
+      <c r="O87" s="66" t="n">
+        <v>16</v>
+      </c>
+      <c r="P87" s="66" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q87" s="66" t="n">
+        <v>12</v>
+      </c>
+      <c r="R87" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S87" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T87" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U87" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="62" customHeight="1" s="29">
+      <c r="A88" s="66" t="n">
+        <v>91</v>
+      </c>
+      <c r="B88" s="67">
+        <f>SUM(N88:Q88)</f>
         <v/>
       </c>
-    </row>
-    <row r="89" ht="15" customHeight="1" s="29">
-      <c r="A89" s="48" t="inlineStr">
-        <is>
-          <t>Liens vérifiés techniquement</t>
-        </is>
-      </c>
-      <c r="B89" s="48">
-        <f>COUNTIF(T5:T76,"Oui*")+COUNTIF(T5:T76,"Non, mention*")</f>
+      <c r="C88" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D88" s="62" t="inlineStr">
+        <is>
+          <t>Vegeto Textiles</t>
+        </is>
+      </c>
+      <c r="E88" s="63" t="inlineStr">
+        <is>
+          <t>https://vegetotextiles.com/en/milkweed/</t>
+        </is>
+      </c>
+      <c r="F88" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, filiere</t>
+        </is>
+      </c>
+      <c r="G88" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H88" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « filiere ».</t>
+        </is>
+      </c>
+      <c r="I88" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J88" s="64" t="inlineStr">
+        <is>
+          <t>Acteur voisin de la filière. Citation mutuelle sur la ressource, pas d'échange commercial.</t>
+        </is>
+      </c>
+      <c r="K88" s="64" t="inlineStr">
+        <is>
+          <t>info@vegetotextiles.com</t>
+        </is>
+      </c>
+      <c r="L88" s="64" t="inlineStr">
+        <is>
+          <t>Confirmé (trouvé sur la page)</t>
+        </is>
+      </c>
+      <c r="M88" s="64" t="inlineStr"/>
+      <c r="N88" s="66" t="n">
+        <v>28</v>
+      </c>
+      <c r="O88" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="P88" s="66" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q88" s="66" t="n">
+        <v>11</v>
+      </c>
+      <c r="R88" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S88" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T88" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U88" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="62" customHeight="1" s="29">
+      <c r="A89" s="66" t="n">
+        <v>45</v>
+      </c>
+      <c r="B89" s="67">
+        <f>SUM(N89:Q89)</f>
         <v/>
       </c>
+      <c r="C89" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D89" s="62" t="inlineStr">
+        <is>
+          <t>La Voix de l'Est (Eko-Terre, 2020)</t>
+        </is>
+      </c>
+      <c r="E89" s="63" t="inlineStr">
+        <is>
+          <t>https://www.lavoixdelest.ca/2020/07/04/eko-terre-se-lance-dans-lasclepiade-16afb8b96791ccda5a56dfea345582fe/</t>
+        </is>
+      </c>
+      <c r="F89" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, presse</t>
+        </is>
+      </c>
+      <c r="G89" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H89" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « presse ».</t>
+        </is>
+      </c>
+      <c r="I89" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J89" s="64" t="inlineStr">
+        <is>
+          <t>Article sur la filière. Se rendre disponible comme source pour la prochaine couverture, en écrivant directement à la ou au signataire.</t>
+        </is>
+      </c>
+      <c r="K89" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L89" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M89" s="64" t="inlineStr"/>
+      <c r="N89" s="66" t="n">
+        <v>25</v>
+      </c>
+      <c r="O89" s="66" t="n">
+        <v>21</v>
+      </c>
+      <c r="P89" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q89" s="66" t="n">
+        <v>14</v>
+      </c>
+      <c r="R89" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S89" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T89" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U89" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="62" customHeight="1" s="29">
+      <c r="A90" s="66" t="n">
+        <v>46</v>
+      </c>
+      <c r="B90" s="67">
+        <f>SUM(N90:Q90)</f>
+        <v/>
+      </c>
+      <c r="C90" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D90" s="62" t="inlineStr">
+        <is>
+          <t>La Voix de l'Est (Vegeto, 2021)</t>
+        </is>
+      </c>
+      <c r="E90" s="63" t="inlineStr">
+        <is>
+          <t>https://www.lavoixdelest.ca/2021/04/02/la-fibre-dasclepiade-devient-vegeto-b277caf08ef272d82887a1bd1d8d4dde/</t>
+        </is>
+      </c>
+      <c r="F90" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, presse</t>
+        </is>
+      </c>
+      <c r="G90" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H90" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « presse ».</t>
+        </is>
+      </c>
+      <c r="I90" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J90" s="64" t="inlineStr">
+        <is>
+          <t>Article sur la filière. Se rendre disponible comme source pour la prochaine couverture, en écrivant directement à la ou au signataire.</t>
+        </is>
+      </c>
+      <c r="K90" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L90" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M90" s="64" t="inlineStr"/>
+      <c r="N90" s="66" t="n">
+        <v>25</v>
+      </c>
+      <c r="O90" s="66" t="n">
+        <v>21</v>
+      </c>
+      <c r="P90" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q90" s="66" t="n">
+        <v>14</v>
+      </c>
+      <c r="R90" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S90" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T90" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U90" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="62" customHeight="1" s="29">
+      <c r="A91" s="66" t="n">
+        <v>47</v>
+      </c>
+      <c r="B91" s="67">
+        <f>SUM(N91:Q91)</f>
+        <v/>
+      </c>
+      <c r="C91" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D91" s="62" t="inlineStr">
+        <is>
+          <t>La Tribune (Vegeto, 2021)</t>
+        </is>
+      </c>
+      <c r="E91" s="63" t="inlineStr">
+        <is>
+          <t>https://www.latribune.ca/2021/04/02/la-fibre-dasclepiade-devient-vegeto-b277caf08ef272d82887a1bd1d8d4dde/</t>
+        </is>
+      </c>
+      <c r="F91" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, presse</t>
+        </is>
+      </c>
+      <c r="G91" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H91" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « presse ».</t>
+        </is>
+      </c>
+      <c r="I91" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J91" s="64" t="inlineStr">
+        <is>
+          <t>Article sur la filière. Se rendre disponible comme source pour la prochaine couverture, en écrivant directement à la ou au signataire.</t>
+        </is>
+      </c>
+      <c r="K91" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L91" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M91" s="64" t="inlineStr"/>
+      <c r="N91" s="66" t="n">
+        <v>25</v>
+      </c>
+      <c r="O91" s="66" t="n">
+        <v>21</v>
+      </c>
+      <c r="P91" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q91" s="66" t="n">
+        <v>14</v>
+      </c>
+      <c r="R91" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S91" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T91" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U91" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="62" customHeight="1" s="29">
+      <c r="A92" s="66" t="n">
+        <v>48</v>
+      </c>
+      <c r="B92" s="67">
+        <f>SUM(N92:Q92)</f>
+        <v/>
+      </c>
+      <c r="C92" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D92" s="62" t="inlineStr">
+        <is>
+          <t>La Tribune (premiers manteaux, 2016)</t>
+        </is>
+      </c>
+      <c r="E92" s="63" t="inlineStr">
+        <is>
+          <t>https://www.latribune.ca/2016/10/18/deux-premiers-manteaux-dhiver-isoles-alasclepiade-dici-sont-lances-1fe354379dc11b9e0b261b091509c2a1/</t>
+        </is>
+      </c>
+      <c r="F92" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, presse</t>
+        </is>
+      </c>
+      <c r="G92" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H92" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « presse ».</t>
+        </is>
+      </c>
+      <c r="I92" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J92" s="64" t="inlineStr">
+        <is>
+          <t>Article sur la filière. Se rendre disponible comme source pour la prochaine couverture, en écrivant directement à la ou au signataire.</t>
+        </is>
+      </c>
+      <c r="K92" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L92" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M92" s="64" t="inlineStr"/>
+      <c r="N92" s="66" t="n">
+        <v>25</v>
+      </c>
+      <c r="O92" s="66" t="n">
+        <v>21</v>
+      </c>
+      <c r="P92" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q92" s="66" t="n">
+        <v>14</v>
+      </c>
+      <c r="R92" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S92" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T92" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U92" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="62" customHeight="1" s="29">
+      <c r="A93" s="66" t="n">
+        <v>28</v>
+      </c>
+      <c r="B93" s="67">
+        <f>SUM(N93:Q93)</f>
+        <v/>
+      </c>
+      <c r="C93" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D93" s="62" t="inlineStr">
+        <is>
+          <t>Le Quotidien (deuxième vie, 2020)</t>
+        </is>
+      </c>
+      <c r="E93" s="63" t="inlineStr">
+        <is>
+          <t>https://www.lequotidien.com/2020/10/09/la-deuxieme-vie-de-lasclepiade-0f31e3d5aaa1770d7f092c6d46c5a2e2/</t>
+        </is>
+      </c>
+      <c r="F93" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, presse</t>
+        </is>
+      </c>
+      <c r="G93" s="64" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H93" s="64" t="inlineStr">
+        <is>
+          <t>La page nomme Lasclay.</t>
+        </is>
+      </c>
+      <c r="I93" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J93" s="64" t="inlineStr">
+        <is>
+          <t>Article sur la filière. Se rendre disponible comme source pour la prochaine couverture, en écrivant directement à la ou au signataire.</t>
+        </is>
+      </c>
+      <c r="K93" s="64" t="inlineStr">
+        <is>
+          <t>groy@lequotidien.com</t>
+        </is>
+      </c>
+      <c r="L93" s="64" t="inlineStr">
+        <is>
+          <t>Confirmé (trouvé sur la page)</t>
+        </is>
+      </c>
+      <c r="M93" s="64" t="inlineStr"/>
+      <c r="N93" s="66" t="n">
+        <v>25</v>
+      </c>
+      <c r="O93" s="66" t="n">
+        <v>21</v>
+      </c>
+      <c r="P93" s="66" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q93" s="66" t="n">
+        <v>14</v>
+      </c>
+      <c r="R93" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S93" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T93" s="71" t="inlineStr">
+        <is>
+          <t>NON, mention présente sans lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U93" s="64" t="inlineStr">
+        <is>
+          <t>Occasion confirmée. Demander l'ajout du lien sur la mention existante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="62" customHeight="1" s="29">
+      <c r="A94" s="66" t="n">
+        <v>49</v>
+      </c>
+      <c r="B94" s="67">
+        <f>SUM(N94:Q94)</f>
+        <v/>
+      </c>
+      <c r="C94" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D94" s="62" t="inlineStr">
+        <is>
+          <t>Le Droit (monarques et manteaux, 2018)</t>
+        </is>
+      </c>
+      <c r="E94" s="63" t="inlineStr">
+        <is>
+          <t>https://www.ledroit.com/2018/08/22/lasclepiade-pour-aider-les-monarques-et-fabriquer-des-manteaux-dhiver-840420f683cdf7801cacbb70e3f28809/</t>
+        </is>
+      </c>
+      <c r="F94" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, presse</t>
+        </is>
+      </c>
+      <c r="G94" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H94" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « presse ».</t>
+        </is>
+      </c>
+      <c r="I94" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J94" s="64" t="inlineStr">
+        <is>
+          <t>Article sur la filière. Se rendre disponible comme source pour la prochaine couverture, en écrivant directement à la ou au signataire.</t>
+        </is>
+      </c>
+      <c r="K94" s="64" t="inlineStr">
+        <is>
+          <t>lgelinas@lesoleil.com</t>
+        </is>
+      </c>
+      <c r="L94" s="64" t="inlineStr">
+        <is>
+          <t>Confirmé (trouvé sur la page)</t>
+        </is>
+      </c>
+      <c r="M94" s="64" t="inlineStr"/>
+      <c r="N94" s="66" t="n">
+        <v>25</v>
+      </c>
+      <c r="O94" s="66" t="n">
+        <v>21</v>
+      </c>
+      <c r="P94" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q94" s="66" t="n">
+        <v>14</v>
+      </c>
+      <c r="R94" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S94" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T94" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U94" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="62" customHeight="1" s="29">
+      <c r="A95" s="66" t="n">
+        <v>50</v>
+      </c>
+      <c r="B95" s="67">
+        <f>SUM(N95:Q95)</f>
+        <v/>
+      </c>
+      <c r="C95" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D95" s="62" t="inlineStr">
+        <is>
+          <t>Radio-Canada (premier manteau)</t>
+        </is>
+      </c>
+      <c r="E95" s="63" t="inlineStr">
+        <is>
+          <t>https://ici.radio-canada.ca/nouvelle/808202/premier-manteau-asclepiade-marche-quartz-soie-amerique</t>
+        </is>
+      </c>
+      <c r="F95" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, presse</t>
+        </is>
+      </c>
+      <c r="G95" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H95" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « presse ».</t>
+        </is>
+      </c>
+      <c r="I95" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J95" s="64" t="inlineStr">
+        <is>
+          <t>Article sur la filière. Se rendre disponible comme source pour la prochaine couverture, en écrivant directement à la ou au signataire.</t>
+        </is>
+      </c>
+      <c r="K95" s="64" t="inlineStr">
+        <is>
+          <t>vincent.maisonneuve@radio-canada.ca</t>
+        </is>
+      </c>
+      <c r="L95" s="64" t="inlineStr">
+        <is>
+          <t>Confirmé (trouvé sur la page)</t>
+        </is>
+      </c>
+      <c r="M95" s="64" t="inlineStr"/>
+      <c r="N95" s="66" t="n">
+        <v>25</v>
+      </c>
+      <c r="O95" s="66" t="n">
+        <v>21</v>
+      </c>
+      <c r="P95" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q95" s="66" t="n">
+        <v>14</v>
+      </c>
+      <c r="R95" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S95" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T95" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U95" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="62" customHeight="1" s="29">
+      <c r="A96" s="66" t="n">
+        <v>51</v>
+      </c>
+      <c r="B96" s="67">
+        <f>SUM(N96:Q96)</f>
+        <v/>
+      </c>
+      <c r="C96" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D96" s="62" t="inlineStr">
+        <is>
+          <t>Radio-Canada (production industrielle)</t>
+        </is>
+      </c>
+      <c r="E96" s="63" t="inlineStr">
+        <is>
+          <t>https://ici.radio-canada.ca/nouvelle/745682/asclepiade-soie-amerique-production-recolte-soyer-du-quebec</t>
+        </is>
+      </c>
+      <c r="F96" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, presse</t>
+        </is>
+      </c>
+      <c r="G96" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H96" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « presse ».</t>
+        </is>
+      </c>
+      <c r="I96" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J96" s="64" t="inlineStr">
+        <is>
+          <t>Article sur la filière. Se rendre disponible comme source pour la prochaine couverture, en écrivant directement à la ou au signataire.</t>
+        </is>
+      </c>
+      <c r="K96" s="64" t="inlineStr">
+        <is>
+          <t>jean-michel.leprince@radio-canada.ca</t>
+        </is>
+      </c>
+      <c r="L96" s="64" t="inlineStr">
+        <is>
+          <t>Confirmé (trouvé sur la page)</t>
+        </is>
+      </c>
+      <c r="M96" s="64" t="inlineStr"/>
+      <c r="N96" s="66" t="n">
+        <v>25</v>
+      </c>
+      <c r="O96" s="66" t="n">
+        <v>21</v>
+      </c>
+      <c r="P96" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q96" s="66" t="n">
+        <v>14</v>
+      </c>
+      <c r="R96" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S96" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T96" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U96" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="62" customHeight="1" s="29">
+      <c r="A97" s="66" t="n">
+        <v>52</v>
+      </c>
+      <c r="B97" s="67">
+        <f>SUM(N97:Q97)</f>
+        <v/>
+      </c>
+      <c r="C97" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D97" s="62" t="inlineStr">
+        <is>
+          <t>Radio-Canada (eldorado)</t>
+        </is>
+      </c>
+      <c r="E97" s="63" t="inlineStr">
+        <is>
+          <t>https://ici.radio-canada.ca/nouvelle/689991/asclepiade-soie-amerique-test-quebec-vetements</t>
+        </is>
+      </c>
+      <c r="F97" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, presse</t>
+        </is>
+      </c>
+      <c r="G97" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H97" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « presse ».</t>
+        </is>
+      </c>
+      <c r="I97" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J97" s="64" t="inlineStr">
+        <is>
+          <t>Article sur la filière. Se rendre disponible comme source pour la prochaine couverture, en écrivant directement à la ou au signataire.</t>
+        </is>
+      </c>
+      <c r="K97" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L97" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M97" s="64" t="inlineStr"/>
+      <c r="N97" s="66" t="n">
+        <v>25</v>
+      </c>
+      <c r="O97" s="66" t="n">
+        <v>21</v>
+      </c>
+      <c r="P97" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q97" s="66" t="n">
+        <v>14</v>
+      </c>
+      <c r="R97" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S97" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T97" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U97" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="62" customHeight="1" s="29">
+      <c r="A98" s="66" t="n">
+        <v>53</v>
+      </c>
+      <c r="B98" s="67">
+        <f>SUM(N98:Q98)</f>
+        <v/>
+      </c>
+      <c r="C98" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D98" s="62" t="inlineStr">
+        <is>
+          <t>Radio-Canada (Encore 3, St-Tite)</t>
+        </is>
+      </c>
+      <c r="E98" s="63" t="inlineStr">
+        <is>
+          <t>https://ici.radio-canada.ca/nouvelle/1070305/asclepiade-manteau-isolant-plante-soyer-quebec-encore3-st-tite-mauricie</t>
+        </is>
+      </c>
+      <c r="F98" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, presse</t>
+        </is>
+      </c>
+      <c r="G98" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H98" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « presse ».</t>
+        </is>
+      </c>
+      <c r="I98" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J98" s="64" t="inlineStr">
+        <is>
+          <t>Article sur la filière. Se rendre disponible comme source pour la prochaine couverture, en écrivant directement à la ou au signataire.</t>
+        </is>
+      </c>
+      <c r="K98" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L98" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M98" s="64" t="inlineStr"/>
+      <c r="N98" s="66" t="n">
+        <v>25</v>
+      </c>
+      <c r="O98" s="66" t="n">
+        <v>21</v>
+      </c>
+      <c r="P98" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q98" s="66" t="n">
+        <v>14</v>
+      </c>
+      <c r="R98" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S98" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T98" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U98" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="62" customHeight="1" s="29">
+      <c r="A99" s="66" t="n">
+        <v>54</v>
+      </c>
+      <c r="B99" s="67">
+        <f>SUM(N99:Q99)</f>
+        <v/>
+      </c>
+      <c r="C99" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D99" s="62" t="inlineStr">
+        <is>
+          <t>Radio-Canada (Bilodeau)</t>
+        </is>
+      </c>
+      <c r="E99" s="63" t="inlineStr">
+        <is>
+          <t>https://ici.radio-canada.ca/nouvelle/1841219/bilodeau-canada-isolant-asclepiade</t>
+        </is>
+      </c>
+      <c r="F99" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, presse</t>
+        </is>
+      </c>
+      <c r="G99" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H99" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « presse ».</t>
+        </is>
+      </c>
+      <c r="I99" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J99" s="64" t="inlineStr">
+        <is>
+          <t>Article sur la filière. Se rendre disponible comme source pour la prochaine couverture, en écrivant directement à la ou au signataire.</t>
+        </is>
+      </c>
+      <c r="K99" s="64" t="inlineStr">
+        <is>
+          <t>annie-claude.brisson@radio-canada.ca</t>
+        </is>
+      </c>
+      <c r="L99" s="64" t="inlineStr">
+        <is>
+          <t>Confirmé (trouvé sur la page)</t>
+        </is>
+      </c>
+      <c r="M99" s="64" t="inlineStr"/>
+      <c r="N99" s="66" t="n">
+        <v>25</v>
+      </c>
+      <c r="O99" s="66" t="n">
+        <v>21</v>
+      </c>
+      <c r="P99" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q99" s="66" t="n">
+        <v>14</v>
+      </c>
+      <c r="R99" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S99" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T99" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U99" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="62" customHeight="1" s="29">
+      <c r="A100" s="66" t="n">
+        <v>55</v>
+      </c>
+      <c r="B100" s="67">
+        <f>SUM(N100:Q100)</f>
+        <v/>
+      </c>
+      <c r="C100" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D100" s="62" t="inlineStr">
+        <is>
+          <t>ICI Explora (soie végétale)</t>
+        </is>
+      </c>
+      <c r="E100" s="63" t="inlineStr">
+        <is>
+          <t>https://ici.exploratv.ca/blogue/une-soie-vegetale-fa/</t>
+        </is>
+      </c>
+      <c r="F100" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, presse</t>
+        </is>
+      </c>
+      <c r="G100" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H100" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « presse ».</t>
+        </is>
+      </c>
+      <c r="I100" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J100" s="64" t="inlineStr">
+        <is>
+          <t>Article sur la filière. Se rendre disponible comme source pour la prochaine couverture, en écrivant directement à la ou au signataire.</t>
+        </is>
+      </c>
+      <c r="K100" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L100" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M100" s="64" t="inlineStr"/>
+      <c r="N100" s="66" t="n">
+        <v>25</v>
+      </c>
+      <c r="O100" s="66" t="n">
+        <v>21</v>
+      </c>
+      <c r="P100" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q100" s="66" t="n">
+        <v>14</v>
+      </c>
+      <c r="R100" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S100" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T100" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U100" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="62" customHeight="1" s="29">
+      <c r="A101" s="60" t="n">
+        <v>11</v>
+      </c>
+      <c r="B101" s="61">
+        <f>SUM(N101:Q101)</f>
+        <v/>
+      </c>
+      <c r="C101" s="61" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D101" s="62" t="inlineStr">
+        <is>
+          <t>Espaces (le soyer du Québec)</t>
+        </is>
+      </c>
+      <c r="E101" s="63" t="inlineStr">
+        <is>
+          <t>https://www.espaces.ca/articles/actualites/1672-le-soyer-du-quebec-la-mauvaise-herbe-qui-remplacera-le-duvet</t>
+        </is>
+      </c>
+      <c r="F101" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, presse plein air</t>
+        </is>
+      </c>
+      <c r="G101" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H101" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « presse plein air ».</t>
+        </is>
+      </c>
+      <c r="I101" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J101" s="64" t="inlineStr">
+        <is>
+          <t>Média plein air très pertinent. Proposer un sujet ou une mise à jour, puis demander le lien.</t>
+        </is>
+      </c>
+      <c r="K101" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L101" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M101" s="64" t="inlineStr"/>
+      <c r="N101" s="60" t="n">
+        <v>28</v>
+      </c>
+      <c r="O101" s="60" t="n">
+        <v>20</v>
+      </c>
+      <c r="P101" s="60" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q101" s="60" t="n">
+        <v>16</v>
+      </c>
+      <c r="R101" s="64" t="inlineStr">
+        <is>
+          <t>À qualifier</t>
+        </is>
+      </c>
+      <c r="S101" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T101" s="70" t="inlineStr">
+        <is>
+          <t>À ouvrir à la main</t>
+        </is>
+      </c>
+      <c r="U101" s="64" t="inlineStr">
+        <is>
+          <t>Le serveur refuse les requêtes automatisées. À ouvrir à la main (HTTP 403)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="62" customHeight="1" s="29">
+      <c r="A102" s="60" t="n">
+        <v>12</v>
+      </c>
+      <c r="B102" s="61">
+        <f>SUM(N102:Q102)</f>
+        <v/>
+      </c>
+      <c r="C102" s="61" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D102" s="62" t="inlineStr">
+        <is>
+          <t>Espaces (manteaux mauvaises herbes)</t>
+        </is>
+      </c>
+      <c r="E102" s="63" t="inlineStr">
+        <is>
+          <t>https://www.espaces.ca/articles/actualites/2556-des-manteaux-fabriques-a-partir-de-mauvaises-herbes-du-quebec</t>
+        </is>
+      </c>
+      <c r="F102" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, presse plein air</t>
+        </is>
+      </c>
+      <c r="G102" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H102" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « presse plein air ».</t>
+        </is>
+      </c>
+      <c r="I102" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J102" s="64" t="inlineStr">
+        <is>
+          <t>Média plein air très pertinent. Proposer un sujet ou une mise à jour, puis demander le lien.</t>
+        </is>
+      </c>
+      <c r="K102" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L102" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M102" s="64" t="inlineStr"/>
+      <c r="N102" s="60" t="n">
+        <v>28</v>
+      </c>
+      <c r="O102" s="60" t="n">
+        <v>20</v>
+      </c>
+      <c r="P102" s="60" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q102" s="60" t="n">
+        <v>16</v>
+      </c>
+      <c r="R102" s="64" t="inlineStr">
+        <is>
+          <t>À qualifier</t>
+        </is>
+      </c>
+      <c r="S102" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T102" s="70" t="inlineStr">
+        <is>
+          <t>À ouvrir à la main</t>
+        </is>
+      </c>
+      <c r="U102" s="64" t="inlineStr">
+        <is>
+          <t>Le serveur refuse les requêtes automatisées. À ouvrir à la main (HTTP 403)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="62" customHeight="1" s="29">
+      <c r="A103" s="66" t="n">
+        <v>59</v>
+      </c>
+      <c r="B103" s="67">
+        <f>SUM(N103:Q103)</f>
+        <v/>
+      </c>
+      <c r="C103" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D103" s="62" t="inlineStr">
+        <is>
+          <t>Altitude Sports (blogue)</t>
+        </is>
+      </c>
+      <c r="E103" s="63" t="inlineStr">
+        <is>
+          <t>https://fr.altitude-sports.com/a/blog/altitude-sports-x-quartz-co-une-urbaine-manteau-dhiver-en-asclepiade/</t>
+        </is>
+      </c>
+      <c r="F103" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, detaillant</t>
+        </is>
+      </c>
+      <c r="G103" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H103" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « detaillant ».</t>
+        </is>
+      </c>
+      <c r="I103" s="64" t="inlineStr">
+        <is>
+          <t>Page d'accueil + collection manteaux</t>
+        </is>
+      </c>
+      <c r="J103" s="64" t="inlineStr">
+        <is>
+          <t>Détaillant qui vend déjà de l'asclépiade. Prospection commerciale d'abord, lien ensuite.</t>
+        </is>
+      </c>
+      <c r="K103" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L103" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M103" s="64" t="inlineStr"/>
+      <c r="N103" s="66" t="n">
+        <v>24</v>
+      </c>
+      <c r="O103" s="66" t="n">
+        <v>17</v>
+      </c>
+      <c r="P103" s="66" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q103" s="66" t="n">
+        <v>14</v>
+      </c>
+      <c r="R103" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S103" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T103" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U103" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="62" customHeight="1" s="29">
+      <c r="A104" s="66" t="n">
+        <v>83</v>
+      </c>
+      <c r="B104" s="67">
+        <f>SUM(N104:Q104)</f>
+        <v/>
+      </c>
+      <c r="C104" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D104" s="62" t="inlineStr">
+        <is>
+          <t>UPA</t>
+        </is>
+      </c>
+      <c r="E104" s="63" t="inlineStr">
+        <is>
+          <t>https://www.upa.qc.ca/producteur/centre-des-communications/nouvelles/toutes-les-nouvelles/mauvaise-herbe-aux-proprietes-royales</t>
+        </is>
+      </c>
+      <c r="F104" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, agricole</t>
+        </is>
+      </c>
+      <c r="G104" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H104" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « agricole ».</t>
+        </is>
+      </c>
+      <c r="I104" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J104" s="64" t="inlineStr">
+        <is>
+          <t>Presse et milieu agricoles. Se rendre disponible comme source sur la filière.</t>
+        </is>
+      </c>
+      <c r="K104" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L104" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M104" s="64" t="inlineStr"/>
+      <c r="N104" s="66" t="n">
+        <v>26</v>
+      </c>
+      <c r="O104" s="66" t="n">
+        <v>18</v>
+      </c>
+      <c r="P104" s="66" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q104" s="66" t="n">
+        <v>11</v>
+      </c>
+      <c r="R104" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S104" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T104" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U104" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="62" customHeight="1" s="29">
+      <c r="A105" s="66" t="n">
+        <v>96</v>
+      </c>
+      <c r="B105" s="67">
+        <f>SUM(N105:Q105)</f>
+        <v/>
+      </c>
+      <c r="C105" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D105" s="62" t="inlineStr">
+        <is>
+          <t>mmode (article Bilodeau)</t>
+        </is>
+      </c>
+      <c r="E105" s="63" t="inlineStr">
+        <is>
+          <t>https://www.mmode.ca/mmodeeco/bilodeau-canada-rien-ne-se-perd-tout-se-transforme</t>
+        </is>
+      </c>
+      <c r="F105" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, mode</t>
+        </is>
+      </c>
+      <c r="G105" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H105" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « mode ».</t>
+        </is>
+      </c>
+      <c r="I105" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J105" s="64" t="inlineStr">
+        <is>
+          <t>Écosystème mode et textile du Québec. Demander une fiche ou un article.</t>
+        </is>
+      </c>
+      <c r="K105" s="64" t="inlineStr">
+        <is>
+          <t>info@mmode.ca</t>
+        </is>
+      </c>
+      <c r="L105" s="64" t="inlineStr">
+        <is>
+          <t>Confirmé (trouvé sur la page)</t>
+        </is>
+      </c>
+      <c r="M105" s="64" t="inlineStr"/>
+      <c r="N105" s="66" t="n">
+        <v>22</v>
+      </c>
+      <c r="O105" s="66" t="n">
+        <v>16</v>
+      </c>
+      <c r="P105" s="66" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q105" s="66" t="n">
+        <v>11</v>
+      </c>
+      <c r="R105" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S105" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T105" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U105" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="62" customHeight="1" s="29">
+      <c r="A106" s="68" t="n">
+        <v>122</v>
+      </c>
+      <c r="B106" s="69">
+        <f>SUM(N106:Q106)</f>
+        <v/>
+      </c>
+      <c r="C106" s="69" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D106" s="62" t="inlineStr">
+        <is>
+          <t>États de Splendeur</t>
+        </is>
+      </c>
+      <c r="E106" s="63" t="inlineStr">
+        <is>
+          <t>https://www.etatsdesplendeur.com/2018/12/27/asclepiade-soyer-du-quebec-fibre-du-futur/</t>
+        </is>
+      </c>
+      <c r="F106" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, blogue</t>
+        </is>
+      </c>
+      <c r="G106" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H106" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « blogue ».</t>
+        </is>
+      </c>
+      <c r="I106" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J106" s="64" t="inlineStr">
+        <is>
+          <t>Blogue indépendant, facile à joindre. Offrir la ressource de plantation.</t>
+        </is>
+      </c>
+      <c r="K106" s="64" t="inlineStr">
+        <is>
+          <t>info@etatsddespleneur.com</t>
+        </is>
+      </c>
+      <c r="L106" s="64" t="inlineStr">
+        <is>
+          <t>Confirmé (trouvé sur la page)</t>
+        </is>
+      </c>
+      <c r="M106" s="64" t="inlineStr">
+        <is>
+          <t>rtailleur2005@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="N106" s="68" t="n">
+        <v>23</v>
+      </c>
+      <c r="O106" s="68" t="n">
+        <v>10</v>
+      </c>
+      <c r="P106" s="68" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q106" s="68" t="n">
+        <v>10</v>
+      </c>
+      <c r="R106" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S106" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T106" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U106" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="62" customHeight="1" s="29">
+      <c r="A107" s="66" t="n">
+        <v>104</v>
+      </c>
+      <c r="B107" s="67">
+        <f>SUM(N107:Q107)</f>
+        <v/>
+      </c>
+      <c r="C107" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D107" s="62" t="inlineStr">
+        <is>
+          <t>Lokta (Martine Gautier)</t>
+        </is>
+      </c>
+      <c r="E107" s="63" t="inlineStr">
+        <is>
+          <t>https://lokta.fr/2022/11/asclepiade-soyer-du-quebec.html</t>
+        </is>
+      </c>
+      <c r="F107" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, artisanat</t>
+        </is>
+      </c>
+      <c r="G107" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H107" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « artisanat ».</t>
+        </is>
+      </c>
+      <c r="I107" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J107" s="64" t="inlineStr">
+        <is>
+          <t>Artisanat de la fibre. Complémentarité réelle, proposer un contenu croisé.</t>
+        </is>
+      </c>
+      <c r="K107" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L107" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M107" s="64" t="inlineStr"/>
+      <c r="N107" s="66" t="n">
+        <v>25</v>
+      </c>
+      <c r="O107" s="66" t="n">
+        <v>10</v>
+      </c>
+      <c r="P107" s="66" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q107" s="66" t="n">
+        <v>10</v>
+      </c>
+      <c r="R107" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S107" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T107" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U107" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="62" customHeight="1" s="29">
+      <c r="A108" s="66" t="n">
+        <v>105</v>
+      </c>
+      <c r="B108" s="67">
+        <f>SUM(N108:Q108)</f>
+        <v/>
+      </c>
+      <c r="C108" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D108" s="62" t="inlineStr">
+        <is>
+          <t>Atelier Retailles (papier d'asclépiade)</t>
+        </is>
+      </c>
+      <c r="E108" s="63" t="inlineStr">
+        <is>
+          <t>https://www.atelierretailles.com/programmation-cours-et-formations/fabrication-de-papier-avec-lasclpiade-de-la-plante-la-feuille</t>
+        </is>
+      </c>
+      <c r="F108" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, artisanat</t>
+        </is>
+      </c>
+      <c r="G108" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H108" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « artisanat ».</t>
+        </is>
+      </c>
+      <c r="I108" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J108" s="64" t="inlineStr">
+        <is>
+          <t>Artisanat de la fibre. Complémentarité réelle, proposer un contenu croisé.</t>
+        </is>
+      </c>
+      <c r="K108" s="64" t="inlineStr">
+        <is>
+          <t>info@atelierretailles.com</t>
+        </is>
+      </c>
+      <c r="L108" s="64" t="inlineStr">
+        <is>
+          <t>Confirmé (trouvé sur la page)</t>
+        </is>
+      </c>
+      <c r="M108" s="64" t="inlineStr"/>
+      <c r="N108" s="66" t="n">
+        <v>25</v>
+      </c>
+      <c r="O108" s="66" t="n">
+        <v>10</v>
+      </c>
+      <c r="P108" s="66" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q108" s="66" t="n">
+        <v>10</v>
+      </c>
+      <c r="R108" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S108" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T108" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U108" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="62" customHeight="1" s="29">
+      <c r="A109" s="66" t="n">
+        <v>115</v>
+      </c>
+      <c r="B109" s="67">
+        <f>SUM(N109:Q109)</f>
+        <v/>
+      </c>
+      <c r="C109" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D109" s="62" t="inlineStr">
+        <is>
+          <t>Textile Blog (EN)</t>
+        </is>
+      </c>
+      <c r="E109" s="63" t="inlineStr">
+        <is>
+          <t>https://www.textileblog.com/milkweed-fiber-properties-processing-and-applications/</t>
+        </is>
+      </c>
+      <c r="F109" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, presse spec EN</t>
+        </is>
+      </c>
+      <c r="G109" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H109" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « presse spec EN ».</t>
+        </is>
+      </c>
+      <c r="I109" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J109" s="64" t="inlineStr">
+        <is>
+          <t>Presse textile anglophone. Proposer un article de fond sur l'isolant d'asclépiade.</t>
+        </is>
+      </c>
+      <c r="K109" s="64" t="inlineStr">
+        <is>
+          <t>mh18.bd@gmail.com</t>
+        </is>
+      </c>
+      <c r="L109" s="64" t="inlineStr">
+        <is>
+          <t>Confirmé (trouvé sur la page)</t>
+        </is>
+      </c>
+      <c r="M109" s="64" t="inlineStr"/>
+      <c r="N109" s="66" t="n">
+        <v>23</v>
+      </c>
+      <c r="O109" s="66" t="n">
+        <v>15</v>
+      </c>
+      <c r="P109" s="66" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q109" s="66" t="n">
+        <v>10</v>
+      </c>
+      <c r="R109" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S109" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T109" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U109" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="62" customHeight="1" s="29">
+      <c r="A110" s="66" t="n">
+        <v>70</v>
+      </c>
+      <c r="B110" s="67">
+        <f>SUM(N110:Q110)</f>
+        <v/>
+      </c>
+      <c r="C110" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D110" s="62" t="inlineStr">
+        <is>
+          <t>Fleurs sauvages du Québec (commune)</t>
+        </is>
+      </c>
+      <c r="E110" s="63" t="inlineStr">
+        <is>
+          <t>https://www.fleursduquebec.com/encyclopedie/1776-asclepiade-commune.html</t>
+        </is>
+      </c>
+      <c r="F110" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, botanique</t>
+        </is>
+      </c>
+      <c r="G110" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H110" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « botanique ».</t>
+        </is>
+      </c>
+      <c r="I110" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J110" s="64" t="inlineStr">
+        <is>
+          <t>Fiche botanique. Proposer la page pilier comme complément sur l'usage de la fibre.</t>
+        </is>
+      </c>
+      <c r="K110" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L110" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M110" s="64" t="inlineStr"/>
+      <c r="N110" s="66" t="n">
+        <v>26</v>
+      </c>
+      <c r="O110" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="P110" s="66" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q110" s="66" t="n">
+        <v>12</v>
+      </c>
+      <c r="R110" s="64" t="inlineStr">
+        <is>
+          <t>À qualifier</t>
+        </is>
+      </c>
+      <c r="S110" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T110" s="70" t="inlineStr">
+        <is>
+          <t>À ouvrir à la main</t>
+        </is>
+      </c>
+      <c r="U110" s="64" t="inlineStr">
+        <is>
+          <t>Le serveur refuse les requêtes automatisées. À ouvrir à la main (ConnectionError)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="62" customHeight="1" s="29">
+      <c r="A111" s="66" t="n">
+        <v>71</v>
+      </c>
+      <c r="B111" s="67">
+        <f>SUM(N111:Q111)</f>
+        <v/>
+      </c>
+      <c r="C111" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D111" s="62" t="inlineStr">
+        <is>
+          <t>Fleurs sauvages du Québec (incarnate)</t>
+        </is>
+      </c>
+      <c r="E111" s="63" t="inlineStr">
+        <is>
+          <t>https://www.fleursduquebec.com/encyclopedie/1827-asclepiade-incarnate.html</t>
+        </is>
+      </c>
+      <c r="F111" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, botanique</t>
+        </is>
+      </c>
+      <c r="G111" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H111" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « botanique ».</t>
+        </is>
+      </c>
+      <c r="I111" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J111" s="64" t="inlineStr">
+        <is>
+          <t>Fiche botanique. Proposer la page pilier comme complément sur l'usage de la fibre.</t>
+        </is>
+      </c>
+      <c r="K111" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L111" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M111" s="64" t="inlineStr"/>
+      <c r="N111" s="66" t="n">
+        <v>26</v>
+      </c>
+      <c r="O111" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="P111" s="66" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q111" s="66" t="n">
+        <v>12</v>
+      </c>
+      <c r="R111" s="64" t="inlineStr">
+        <is>
+          <t>À qualifier</t>
+        </is>
+      </c>
+      <c r="S111" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T111" s="70" t="inlineStr">
+        <is>
+          <t>À ouvrir à la main</t>
+        </is>
+      </c>
+      <c r="U111" s="64" t="inlineStr">
+        <is>
+          <t>Le serveur refuse les requêtes automatisées. À ouvrir à la main (ConnectionError)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="62" customHeight="1" s="29">
+      <c r="A112" s="66" t="n">
+        <v>72</v>
+      </c>
+      <c r="B112" s="67">
+        <f>SUM(N112:Q112)</f>
+        <v/>
+      </c>
+      <c r="C112" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D112" s="62" t="inlineStr">
+        <is>
+          <t>Agora / Histoire vivante</t>
+        </is>
+      </c>
+      <c r="E112" s="63" t="inlineStr">
+        <is>
+          <t>https://hv.agora.qc.ca/dossiers/asclepiade_commune</t>
+        </is>
+      </c>
+      <c r="F112" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, botanique</t>
+        </is>
+      </c>
+      <c r="G112" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H112" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « botanique ».</t>
+        </is>
+      </c>
+      <c r="I112" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J112" s="64" t="inlineStr">
+        <is>
+          <t>Fiche botanique. Proposer la page pilier comme complément sur l'usage de la fibre.</t>
+        </is>
+      </c>
+      <c r="K112" s="64" t="inlineStr">
+        <is>
+          <t>editeurs@agora.ca</t>
+        </is>
+      </c>
+      <c r="L112" s="64" t="inlineStr">
+        <is>
+          <t>Confirmé (trouvé sur la page)</t>
+        </is>
+      </c>
+      <c r="M112" s="64" t="inlineStr"/>
+      <c r="N112" s="66" t="n">
+        <v>26</v>
+      </c>
+      <c r="O112" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="P112" s="66" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q112" s="66" t="n">
+        <v>12</v>
+      </c>
+      <c r="R112" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S112" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T112" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U112" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="62" customHeight="1" s="29">
+      <c r="A113" s="66" t="n">
+        <v>73</v>
+      </c>
+      <c r="B113" s="67">
+        <f>SUM(N113:Q113)</f>
+        <v/>
+      </c>
+      <c r="C113" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D113" s="62" t="inlineStr">
+        <is>
+          <t>Conservation Nature (FR)</t>
+        </is>
+      </c>
+      <c r="E113" s="63" t="inlineStr">
+        <is>
+          <t>https://www.conservation-nature.fr/plantes/asclepias/</t>
+        </is>
+      </c>
+      <c r="F113" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, botanique</t>
+        </is>
+      </c>
+      <c r="G113" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H113" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « botanique ».</t>
+        </is>
+      </c>
+      <c r="I113" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J113" s="64" t="inlineStr">
+        <is>
+          <t>Fiche botanique. Proposer la page pilier comme complément sur l'usage de la fibre.</t>
+        </is>
+      </c>
+      <c r="K113" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L113" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M113" s="64" t="inlineStr"/>
+      <c r="N113" s="66" t="n">
+        <v>26</v>
+      </c>
+      <c r="O113" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="P113" s="66" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q113" s="66" t="n">
+        <v>12</v>
+      </c>
+      <c r="R113" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S113" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T113" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U113" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="62" customHeight="1" s="29">
+      <c r="A114" s="66" t="n">
+        <v>106</v>
+      </c>
+      <c r="B114" s="67">
+        <f>SUM(N114:Q114)</f>
+        <v/>
+      </c>
+      <c r="C114" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D114" s="62" t="inlineStr">
+        <is>
+          <t>Semences Nouveau Monde</t>
+        </is>
+      </c>
+      <c r="E114" s="63" t="inlineStr">
+        <is>
+          <t>https://www.semencesnouveaumonde.com/page-d-articles/ascl%C3%A9piade-commune</t>
+        </is>
+      </c>
+      <c r="F114" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, semencier</t>
+        </is>
+      </c>
+      <c r="G114" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H114" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « semencier ».</t>
+        </is>
+      </c>
+      <c r="I114" s="64" t="inlineStr">
+        <is>
+          <t>Guide de plantation + collection semences</t>
+        </is>
+      </c>
+      <c r="J114" s="64" t="inlineStr">
+        <is>
+          <t>Semencier. Viser la citation du guide de plantation, pas la vente.</t>
+        </is>
+      </c>
+      <c r="K114" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L114" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M114" s="64" t="inlineStr"/>
+      <c r="N114" s="66" t="n">
+        <v>24</v>
+      </c>
+      <c r="O114" s="66" t="n">
+        <v>12</v>
+      </c>
+      <c r="P114" s="66" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q114" s="66" t="n">
+        <v>11</v>
+      </c>
+      <c r="R114" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S114" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T114" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U114" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="62" customHeight="1" s="29">
+      <c r="A115" s="60" t="n">
+        <v>26</v>
+      </c>
+      <c r="B115" s="61">
+        <f>SUM(N115:Q115)</f>
+        <v/>
+      </c>
+      <c r="C115" s="61" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D115" s="62" t="inlineStr">
+        <is>
+          <t>Wikipédia EN, Asclepias syriaca</t>
+        </is>
+      </c>
+      <c r="E115" s="63" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Asclepias_syriaca</t>
+        </is>
+      </c>
+      <c r="F115" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, encyclopedie</t>
+        </is>
+      </c>
+      <c r="G115" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H115" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « encyclopedie ».</t>
+        </is>
+      </c>
+      <c r="I115" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J115" s="64" t="inlineStr">
+        <is>
+          <t>Ne jamais ajouter soi-même un lien commercial. Publier une ressource sourcée et laisser la communauté citer.</t>
+        </is>
+      </c>
+      <c r="K115" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L115" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M115" s="64" t="inlineStr"/>
+      <c r="N115" s="60" t="n">
+        <v>29</v>
+      </c>
+      <c r="O115" s="60" t="n">
+        <v>24</v>
+      </c>
+      <c r="P115" s="60" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q115" s="60" t="n">
+        <v>15</v>
+      </c>
+      <c r="R115" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S115" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T115" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U115" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="62" customHeight="1" s="29">
+      <c r="A116" s="66" t="n">
+        <v>97</v>
+      </c>
+      <c r="B116" s="67">
+        <f>SUM(N116:Q116)</f>
+        <v/>
+      </c>
+      <c r="C116" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D116" s="62" t="inlineStr">
+        <is>
+          <t>Gallica, BnF</t>
+        </is>
+      </c>
+      <c r="E116" s="63" t="inlineStr">
+        <is>
+          <t>https://gallica.bnf.fr/accueil/fr/html/lasclepiade</t>
+        </is>
+      </c>
+      <c r="F116" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, patrimoine</t>
+        </is>
+      </c>
+      <c r="G116" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H116" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « patrimoine ».</t>
+        </is>
+      </c>
+      <c r="I116" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J116" s="64" t="inlineStr">
+        <is>
+          <t>Angle historique. Peu probable mais peu coûteux à tenter.</t>
+        </is>
+      </c>
+      <c r="K116" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L116" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M116" s="64" t="inlineStr"/>
+      <c r="N116" s="66" t="n">
+        <v>24</v>
+      </c>
+      <c r="O116" s="66" t="n">
+        <v>24</v>
+      </c>
+      <c r="P116" s="66" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q116" s="66" t="n">
+        <v>11</v>
+      </c>
+      <c r="R116" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S116" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T116" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U116" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="62" customHeight="1" s="29">
+      <c r="A117" s="66" t="n">
+        <v>74</v>
+      </c>
+      <c r="B117" s="67">
+        <f>SUM(N117:Q117)</f>
+        <v/>
+      </c>
+      <c r="C117" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D117" s="62" t="inlineStr">
+        <is>
+          <t>Espace pour la vie (carnet horticole)</t>
+        </is>
+      </c>
+      <c r="E117" s="63" t="inlineStr">
+        <is>
+          <t>https://espacepourlavie.ca/carnet-horticole/asclepiade-commune</t>
+        </is>
+      </c>
+      <c r="F117" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, institution</t>
+        </is>
+      </c>
+      <c r="G117" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H117" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « institution ».</t>
+        </is>
+      </c>
+      <c r="I117" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J117" s="64" t="inlineStr">
+        <is>
+          <t>Institution publique. Angle éducatif et partenariat, pas commercial.</t>
+        </is>
+      </c>
+      <c r="K117" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L117" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M117" s="64" t="inlineStr"/>
+      <c r="N117" s="66" t="n">
+        <v>25</v>
+      </c>
+      <c r="O117" s="66" t="n">
+        <v>23</v>
+      </c>
+      <c r="P117" s="66" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q117" s="66" t="n">
+        <v>12</v>
+      </c>
+      <c r="R117" s="64" t="inlineStr">
+        <is>
+          <t>À qualifier</t>
+        </is>
+      </c>
+      <c r="S117" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T117" s="70" t="inlineStr">
+        <is>
+          <t>À ouvrir à la main</t>
+        </is>
+      </c>
+      <c r="U117" s="64" t="inlineStr">
+        <is>
+          <t>Le serveur refuse les requêtes automatisées. À ouvrir à la main (HTTP 403)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="62" customHeight="1" s="29">
+      <c r="A118" s="66" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" s="67">
+        <f>SUM(N118:Q118)</f>
+        <v/>
+      </c>
+      <c r="C118" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D118" s="62" t="inlineStr">
+        <is>
+          <t>MFFP jeunesse (monarque)</t>
+        </is>
+      </c>
+      <c r="E118" s="63" t="inlineStr">
+        <is>
+          <t>https://mffp.gouv.qc.ca/jeunesse/monarque/</t>
+        </is>
+      </c>
+      <c r="F118" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, education</t>
+        </is>
+      </c>
+      <c r="G118" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H118" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « education ».</t>
+        </is>
+      </c>
+      <c r="I118" s="64" t="inlineStr">
+        <is>
+          <t>Guide de plantation + page mission</t>
+        </is>
+      </c>
+      <c r="J118" s="64" t="inlineStr">
+        <is>
+          <t>Angle pédagogique. Offrir une trousse et des semences aux enseignants.</t>
+        </is>
+      </c>
+      <c r="K118" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L118" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M118" s="64" t="inlineStr"/>
+      <c r="N118" s="66" t="n">
+        <v>22</v>
+      </c>
+      <c r="O118" s="66" t="n">
+        <v>21</v>
+      </c>
+      <c r="P118" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q118" s="66" t="n">
+        <v>9</v>
+      </c>
+      <c r="R118" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S118" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T118" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U118" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="62" customHeight="1" s="29">
+      <c r="A119" s="66" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" s="67">
+        <f>SUM(N119:Q119)</f>
+        <v/>
+      </c>
+      <c r="C119" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D119" s="62" t="inlineStr">
+        <is>
+          <t>Culture-Éducation (Mission monarque)</t>
+        </is>
+      </c>
+      <c r="E119" s="63" t="inlineStr">
+        <is>
+          <t>https://classe.culture-education.ca/ressources/mission-monarque/</t>
+        </is>
+      </c>
+      <c r="F119" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, education</t>
+        </is>
+      </c>
+      <c r="G119" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H119" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « education ».</t>
+        </is>
+      </c>
+      <c r="I119" s="64" t="inlineStr">
+        <is>
+          <t>Guide de plantation + page mission</t>
+        </is>
+      </c>
+      <c r="J119" s="64" t="inlineStr">
+        <is>
+          <t>Angle pédagogique. Offrir une trousse et des semences aux enseignants.</t>
+        </is>
+      </c>
+      <c r="K119" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L119" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M119" s="64" t="inlineStr"/>
+      <c r="N119" s="66" t="n">
+        <v>22</v>
+      </c>
+      <c r="O119" s="66" t="n">
+        <v>21</v>
+      </c>
+      <c r="P119" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q119" s="66" t="n">
+        <v>9</v>
+      </c>
+      <c r="R119" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S119" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T119" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U119" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="62" customHeight="1" s="29">
+      <c r="A120" s="66" t="n">
+        <v>107</v>
+      </c>
+      <c r="B120" s="67">
+        <f>SUM(N120:Q120)</f>
+        <v/>
+      </c>
+      <c r="C120" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D120" s="62" t="inlineStr">
+        <is>
+          <t>Cultive ta ville</t>
+        </is>
+      </c>
+      <c r="E120" s="63" t="inlineStr">
+        <is>
+          <t>https://cultivetaville.com/encyclopedie/apiculture-urbaine/la-flore-mellifere-spontanee-1/asclepiade/</t>
+        </is>
+      </c>
+      <c r="F120" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, apiculture</t>
+        </is>
+      </c>
+      <c r="G120" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H120" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « apiculture ».</t>
+        </is>
+      </c>
+      <c r="I120" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J120" s="64" t="inlineStr">
+        <is>
+          <t>Filon mellifère, complémentaire et non concurrent. Contenu croisé sur la même plante.</t>
+        </is>
+      </c>
+      <c r="K120" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L120" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M120" s="64" t="inlineStr"/>
+      <c r="N120" s="66" t="n">
+        <v>24</v>
+      </c>
+      <c r="O120" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="P120" s="66" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q120" s="66" t="n">
+        <v>10</v>
+      </c>
+      <c r="R120" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S120" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T120" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U120" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="62" customHeight="1" s="29">
+      <c r="A121" s="68" t="n">
+        <v>123</v>
+      </c>
+      <c r="B121" s="69">
+        <f>SUM(N121:Q121)</f>
+        <v/>
+      </c>
+      <c r="C121" s="69" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D121" s="62" t="inlineStr">
+        <is>
+          <t>Conseils phyto-aroma</t>
+        </is>
+      </c>
+      <c r="E121" s="63" t="inlineStr">
+        <is>
+          <t>https://conseilsphytoaroma.com/2018/07/05/lasclepiade-lherbe-aux-perruches-une-plante-aux-milles-vertues-la-fibre-du-futur-le-soyer-du-quebec/</t>
+        </is>
+      </c>
+      <c r="F121" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, herboristerie</t>
+        </is>
+      </c>
+      <c r="G121" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H121" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « herboristerie ».</t>
+        </is>
+      </c>
+      <c r="I121" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J121" s="64" t="inlineStr">
+        <is>
+          <t>Public curieux de la plante. Offrir la page pilier en complément botanique.</t>
+        </is>
+      </c>
+      <c r="K121" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L121" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M121" s="64" t="inlineStr"/>
+      <c r="N121" s="68" t="n">
+        <v>24</v>
+      </c>
+      <c r="O121" s="68" t="n">
+        <v>10</v>
+      </c>
+      <c r="P121" s="68" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q121" s="68" t="n">
+        <v>10</v>
+      </c>
+      <c r="R121" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S121" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T121" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U121" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="62" customHeight="1" s="29">
+      <c r="A122" s="68" t="n">
+        <v>124</v>
+      </c>
+      <c r="B122" s="69">
+        <f>SUM(N122:Q122)</f>
+        <v/>
+      </c>
+      <c r="C122" s="69" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D122" s="62" t="inlineStr">
+        <is>
+          <t>Vitalité Québec</t>
+        </is>
+      </c>
+      <c r="E122" s="63" t="inlineStr">
+        <is>
+          <t>https://vitalitequebec-magazine.com/flore-sauvage-nutritive-du-printemps/</t>
+        </is>
+      </c>
+      <c r="F122" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, comestible</t>
+        </is>
+      </c>
+      <c r="G122" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H122" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « comestible ».</t>
+        </is>
+      </c>
+      <c r="I122" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J122" s="64" t="inlineStr">
+        <is>
+          <t>Angle alimentaire de la même plante. Contenu croisé, zéro concurrence.</t>
+        </is>
+      </c>
+      <c r="K122" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L122" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M122" s="64" t="inlineStr"/>
+      <c r="N122" s="68" t="n">
+        <v>23</v>
+      </c>
+      <c r="O122" s="68" t="n">
+        <v>11</v>
+      </c>
+      <c r="P122" s="68" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q122" s="68" t="n">
+        <v>10</v>
+      </c>
+      <c r="R122" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S122" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T122" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U122" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="62" customHeight="1" s="29">
+      <c r="A123" s="66" t="n">
+        <v>75</v>
+      </c>
+      <c r="B123" s="67">
+        <f>SUM(N123:Q123)</f>
+        <v/>
+      </c>
+      <c r="C123" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D123" s="62" t="inlineStr">
+        <is>
+          <t>Ville de Québec (monarque)</t>
+        </is>
+      </c>
+      <c r="E123" s="63" t="inlineStr">
+        <is>
+          <t>https://www.ville.quebec.qc.ca/citoyens/environnement/milieux-naturels/monarque.aspx</t>
+        </is>
+      </c>
+      <c r="F123" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, municipal</t>
+        </is>
+      </c>
+      <c r="G123" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H123" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « municipal ».</t>
+        </is>
+      </c>
+      <c r="I123" s="64" t="inlineStr">
+        <is>
+          <t>Guide de plantation de l'asclépiade</t>
+        </is>
+      </c>
+      <c r="J123" s="64" t="inlineStr">
+        <is>
+          <t>Ville amie des monarques. Offrir le guide de plantation comme ressource citoyenne, et des semences pour distribution.</t>
+        </is>
+      </c>
+      <c r="K123" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L123" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M123" s="64" t="inlineStr"/>
+      <c r="N123" s="66" t="n">
+        <v>25</v>
+      </c>
+      <c r="O123" s="66" t="n">
+        <v>19</v>
+      </c>
+      <c r="P123" s="66" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q123" s="66" t="n">
+        <v>10</v>
+      </c>
+      <c r="R123" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S123" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T123" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U123" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="62" customHeight="1" s="29">
+      <c r="A124" s="66" t="n">
+        <v>76</v>
+      </c>
+      <c r="B124" s="67">
+        <f>SUM(N124:Q124)</f>
+        <v/>
+      </c>
+      <c r="C124" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D124" s="62" t="inlineStr">
+        <is>
+          <t>Ville de Candiac</t>
+        </is>
+      </c>
+      <c r="E124" s="63" t="inlineStr">
+        <is>
+          <t>https://candiac.ca/developpementdurable/changements-climatiques/ville-amie-des-monarques</t>
+        </is>
+      </c>
+      <c r="F124" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, municipal</t>
+        </is>
+      </c>
+      <c r="G124" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H124" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « municipal ».</t>
+        </is>
+      </c>
+      <c r="I124" s="64" t="inlineStr">
+        <is>
+          <t>Guide de plantation de l'asclépiade</t>
+        </is>
+      </c>
+      <c r="J124" s="64" t="inlineStr">
+        <is>
+          <t>Ville amie des monarques. Offrir le guide de plantation comme ressource citoyenne, et des semences pour distribution.</t>
+        </is>
+      </c>
+      <c r="K124" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L124" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M124" s="64" t="inlineStr"/>
+      <c r="N124" s="66" t="n">
+        <v>25</v>
+      </c>
+      <c r="O124" s="66" t="n">
+        <v>19</v>
+      </c>
+      <c r="P124" s="66" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q124" s="66" t="n">
+        <v>10</v>
+      </c>
+      <c r="R124" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S124" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T124" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U124" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="62" customHeight="1" s="29">
+      <c r="A125" s="66" t="n">
+        <v>77</v>
+      </c>
+      <c r="B125" s="67">
+        <f>SUM(N125:Q125)</f>
+        <v/>
+      </c>
+      <c r="C125" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D125" s="62" t="inlineStr">
+        <is>
+          <t>Ville de Saguenay</t>
+        </is>
+      </c>
+      <c r="E125" s="63" t="inlineStr">
+        <is>
+          <t>https://ville.saguenay.ca/services-aux-citoyens/environnement/developpement-durable/ville-amie-des-monarques</t>
+        </is>
+      </c>
+      <c r="F125" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, municipal</t>
+        </is>
+      </c>
+      <c r="G125" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H125" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « municipal ».</t>
+        </is>
+      </c>
+      <c r="I125" s="64" t="inlineStr">
+        <is>
+          <t>Guide de plantation de l'asclépiade</t>
+        </is>
+      </c>
+      <c r="J125" s="64" t="inlineStr">
+        <is>
+          <t>Ville amie des monarques. Offrir le guide de plantation comme ressource citoyenne, et des semences pour distribution.</t>
+        </is>
+      </c>
+      <c r="K125" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L125" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M125" s="64" t="inlineStr"/>
+      <c r="N125" s="66" t="n">
+        <v>25</v>
+      </c>
+      <c r="O125" s="66" t="n">
+        <v>19</v>
+      </c>
+      <c r="P125" s="66" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q125" s="66" t="n">
+        <v>10</v>
+      </c>
+      <c r="R125" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S125" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T125" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U125" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="62" customHeight="1" s="29">
+      <c r="A126" s="66" t="n">
+        <v>78</v>
+      </c>
+      <c r="B126" s="67">
+        <f>SUM(N126:Q126)</f>
+        <v/>
+      </c>
+      <c r="C126" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D126" s="62" t="inlineStr">
+        <is>
+          <t>Ville de Mercier</t>
+        </is>
+      </c>
+      <c r="E126" s="63" t="inlineStr">
+        <is>
+          <t>https://www.ville.mercier.qc.ca/communique/mercier-ville-amie-des-monarques/</t>
+        </is>
+      </c>
+      <c r="F126" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, municipal</t>
+        </is>
+      </c>
+      <c r="G126" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H126" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « municipal ».</t>
+        </is>
+      </c>
+      <c r="I126" s="64" t="inlineStr">
+        <is>
+          <t>Guide de plantation de l'asclépiade</t>
+        </is>
+      </c>
+      <c r="J126" s="64" t="inlineStr">
+        <is>
+          <t>Ville amie des monarques. Offrir le guide de plantation comme ressource citoyenne, et des semences pour distribution.</t>
+        </is>
+      </c>
+      <c r="K126" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L126" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M126" s="64" t="inlineStr"/>
+      <c r="N126" s="66" t="n">
+        <v>25</v>
+      </c>
+      <c r="O126" s="66" t="n">
+        <v>19</v>
+      </c>
+      <c r="P126" s="66" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q126" s="66" t="n">
+        <v>10</v>
+      </c>
+      <c r="R126" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S126" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T126" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U126" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="62" customHeight="1" s="29">
+      <c r="A127" s="68" t="n">
+        <v>129</v>
+      </c>
+      <c r="B127" s="69">
+        <f>SUM(N127:Q127)</f>
+        <v/>
+      </c>
+      <c r="C127" s="69" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D127" s="62" t="inlineStr">
+        <is>
+          <t>L'Éveil (Oka)</t>
+        </is>
+      </c>
+      <c r="E127" s="63" t="inlineStr">
+        <is>
+          <t>https://leveil.com/actualites/la-municipalite-doka-devient-ville-amie-des-monarques</t>
+        </is>
+      </c>
+      <c r="F127" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, presse locale</t>
+        </is>
+      </c>
+      <c r="G127" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H127" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « presse locale ».</t>
+        </is>
+      </c>
+      <c r="I127" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J127" s="64" t="inlineStr">
+        <is>
+          <t>Média local accessible. Offrir la ressource de plantation et un angle régional.</t>
+        </is>
+      </c>
+      <c r="K127" s="64" t="inlineStr">
+        <is>
+          <t>casselin@groupejcl.ca</t>
+        </is>
+      </c>
+      <c r="L127" s="64" t="inlineStr">
+        <is>
+          <t>Confirmé (trouvé sur la page)</t>
+        </is>
+      </c>
+      <c r="M127" s="64" t="inlineStr">
+        <is>
+          <t>leveil@groupejcl.ca</t>
+        </is>
+      </c>
+      <c r="N127" s="68" t="n">
+        <v>22</v>
+      </c>
+      <c r="O127" s="68" t="n">
+        <v>12</v>
+      </c>
+      <c r="P127" s="68" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q127" s="68" t="n">
+        <v>9</v>
+      </c>
+      <c r="R127" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S127" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T127" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U127" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="62" customHeight="1" s="29">
+      <c r="A128" s="68" t="n">
+        <v>130</v>
+      </c>
+      <c r="B128" s="69">
+        <f>SUM(N128:Q128)</f>
+        <v/>
+      </c>
+      <c r="C128" s="69" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D128" s="62" t="inlineStr">
+        <is>
+          <t>Journal des Citoyens</t>
+        </is>
+      </c>
+      <c r="E128" s="63" t="inlineStr">
+        <is>
+          <t>https://www.jdc.quebec/2022/05/24/oasis-pour-les-monarques/</t>
+        </is>
+      </c>
+      <c r="F128" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, presse locale</t>
+        </is>
+      </c>
+      <c r="G128" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H128" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « presse locale ».</t>
+        </is>
+      </c>
+      <c r="I128" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J128" s="64" t="inlineStr">
+        <is>
+          <t>Média local accessible. Offrir la ressource de plantation et un angle régional.</t>
+        </is>
+      </c>
+      <c r="K128" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L128" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M128" s="64" t="inlineStr"/>
+      <c r="N128" s="68" t="n">
+        <v>22</v>
+      </c>
+      <c r="O128" s="68" t="n">
+        <v>12</v>
+      </c>
+      <c r="P128" s="68" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q128" s="68" t="n">
+        <v>9</v>
+      </c>
+      <c r="R128" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S128" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T128" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U128" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="62" customHeight="1" s="29">
+      <c r="A129" s="66" t="n">
+        <v>108</v>
+      </c>
+      <c r="B129" s="67">
+        <f>SUM(N129:Q129)</f>
+        <v/>
+      </c>
+      <c r="C129" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D129" s="62" t="inlineStr">
+        <is>
+          <t>L'Hebdo du St-Maurice (miel)</t>
+        </is>
+      </c>
+      <c r="E129" s="63" t="inlineStr">
+        <is>
+          <t>https://www.lhebdodustmaurice.com/actualite/miel-dasclepiade-une-premiere-en-amerique-du-nord/</t>
+        </is>
+      </c>
+      <c r="F129" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, apiculture</t>
+        </is>
+      </c>
+      <c r="G129" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H129" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « apiculture ».</t>
+        </is>
+      </c>
+      <c r="I129" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J129" s="64" t="inlineStr">
+        <is>
+          <t>Filon mellifère, complémentaire et non concurrent. Contenu croisé sur la même plante.</t>
+        </is>
+      </c>
+      <c r="K129" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L129" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M129" s="64" t="inlineStr"/>
+      <c r="N129" s="66" t="n">
+        <v>24</v>
+      </c>
+      <c r="O129" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="P129" s="66" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q129" s="66" t="n">
+        <v>10</v>
+      </c>
+      <c r="R129" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S129" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T129" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U129" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="62" customHeight="1" s="29">
+      <c r="A130" s="66" t="n">
+        <v>109</v>
+      </c>
+      <c r="B130" s="67">
+        <f>SUM(N130:Q130)</f>
+        <v/>
+      </c>
+      <c r="C130" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D130" s="62" t="inlineStr">
+        <is>
+          <t>La Terre de chez nous (miel)</t>
+        </is>
+      </c>
+      <c r="E130" s="63" t="inlineStr">
+        <is>
+          <t>https://www.laterre.ca/actualites/lasclepiade-conquiert-marche-miel/</t>
+        </is>
+      </c>
+      <c r="F130" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, apiculture</t>
+        </is>
+      </c>
+      <c r="G130" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H130" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « apiculture ».</t>
+        </is>
+      </c>
+      <c r="I130" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J130" s="64" t="inlineStr">
+        <is>
+          <t>Filon mellifère, complémentaire et non concurrent. Contenu croisé sur la même plante.</t>
+        </is>
+      </c>
+      <c r="K130" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L130" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M130" s="64" t="inlineStr"/>
+      <c r="N130" s="66" t="n">
+        <v>24</v>
+      </c>
+      <c r="O130" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="P130" s="66" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q130" s="66" t="n">
+        <v>10</v>
+      </c>
+      <c r="R130" s="64" t="inlineStr">
+        <is>
+          <t>À qualifier</t>
+        </is>
+      </c>
+      <c r="S130" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T130" s="70" t="inlineStr">
+        <is>
+          <t>À ouvrir à la main</t>
+        </is>
+      </c>
+      <c r="U130" s="64" t="inlineStr">
+        <is>
+          <t>Le serveur refuse les requêtes automatisées. À ouvrir à la main (HTTP 403)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="62" customHeight="1" s="29">
+      <c r="A131" s="66" t="n">
+        <v>110</v>
+      </c>
+      <c r="B131" s="67">
+        <f>SUM(N131:Q131)</f>
+        <v/>
+      </c>
+      <c r="C131" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D131" s="62" t="inlineStr">
+        <is>
+          <t>La Centrale agricole</t>
+        </is>
+      </c>
+      <c r="E131" s="63" t="inlineStr">
+        <is>
+          <t>https://centrale.coop/asclepiade-apiculture/</t>
+        </is>
+      </c>
+      <c r="F131" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, apiculture</t>
+        </is>
+      </c>
+      <c r="G131" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H131" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « apiculture ».</t>
+        </is>
+      </c>
+      <c r="I131" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J131" s="64" t="inlineStr">
+        <is>
+          <t>Filon mellifère, complémentaire et non concurrent. Contenu croisé sur la même plante.</t>
+        </is>
+      </c>
+      <c r="K131" s="64" t="inlineStr">
+        <is>
+          <t>asclepiade.apiculture@gmail.com</t>
+        </is>
+      </c>
+      <c r="L131" s="64" t="inlineStr">
+        <is>
+          <t>Confirmé (trouvé sur la page)</t>
+        </is>
+      </c>
+      <c r="M131" s="64" t="inlineStr"/>
+      <c r="N131" s="66" t="n">
+        <v>24</v>
+      </c>
+      <c r="O131" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="P131" s="66" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q131" s="66" t="n">
+        <v>10</v>
+      </c>
+      <c r="R131" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S131" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T131" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U131" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="62" customHeight="1" s="29">
+      <c r="A132" s="66" t="n">
+        <v>111</v>
+      </c>
+      <c r="B132" s="67">
+        <f>SUM(N132:Q132)</f>
+        <v/>
+      </c>
+      <c r="C132" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D132" s="62" t="inlineStr">
+        <is>
+          <t>Hapiculture (FR)</t>
+        </is>
+      </c>
+      <c r="E132" s="63" t="inlineStr">
+        <is>
+          <t>https://hapiculture.fr/asclepiade-une-plante-mellifere-aux-multiples-facettes/</t>
+        </is>
+      </c>
+      <c r="F132" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, apiculture</t>
+        </is>
+      </c>
+      <c r="G132" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H132" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « apiculture ».</t>
+        </is>
+      </c>
+      <c r="I132" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J132" s="64" t="inlineStr">
+        <is>
+          <t>Filon mellifère, complémentaire et non concurrent. Contenu croisé sur la même plante.</t>
+        </is>
+      </c>
+      <c r="K132" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L132" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M132" s="64" t="inlineStr"/>
+      <c r="N132" s="66" t="n">
+        <v>24</v>
+      </c>
+      <c r="O132" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="P132" s="66" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q132" s="66" t="n">
+        <v>10</v>
+      </c>
+      <c r="R132" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S132" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T132" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U132" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="62" customHeight="1" s="29">
+      <c r="A133" s="66" t="n">
+        <v>84</v>
+      </c>
+      <c r="B133" s="67">
+        <f>SUM(N133:Q133)</f>
+        <v/>
+      </c>
+      <c r="C133" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D133" s="62" t="inlineStr">
+        <is>
+          <t>La Terre (faillite acheteur)</t>
+        </is>
+      </c>
+      <c r="E133" s="63" t="inlineStr">
+        <is>
+          <t>https://www.laterre.ca/actualites/vie-rurale/principal-acheteur-dasclepiade-faillite-producteurs-soulages/</t>
+        </is>
+      </c>
+      <c r="F133" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, agricole</t>
+        </is>
+      </c>
+      <c r="G133" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H133" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « agricole ».</t>
+        </is>
+      </c>
+      <c r="I133" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J133" s="64" t="inlineStr">
+        <is>
+          <t>Presse et milieu agricoles. Se rendre disponible comme source sur la filière.</t>
+        </is>
+      </c>
+      <c r="K133" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L133" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M133" s="64" t="inlineStr"/>
+      <c r="N133" s="66" t="n">
+        <v>26</v>
+      </c>
+      <c r="O133" s="66" t="n">
+        <v>18</v>
+      </c>
+      <c r="P133" s="66" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q133" s="66" t="n">
+        <v>11</v>
+      </c>
+      <c r="R133" s="64" t="inlineStr">
+        <is>
+          <t>À qualifier</t>
+        </is>
+      </c>
+      <c r="S133" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T133" s="70" t="inlineStr">
+        <is>
+          <t>À ouvrir à la main</t>
+        </is>
+      </c>
+      <c r="U133" s="64" t="inlineStr">
+        <is>
+          <t>Le serveur refuse les requêtes automatisées. À ouvrir à la main (HTTP 403)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="62" customHeight="1" s="29">
+      <c r="A134" s="66" t="n">
+        <v>85</v>
+      </c>
+      <c r="B134" s="67">
+        <f>SUM(N134:Q134)</f>
+        <v/>
+      </c>
+      <c r="C134" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D134" s="62" t="inlineStr">
+        <is>
+          <t>La Terre (bisbille production)</t>
+        </is>
+      </c>
+      <c r="E134" s="63" t="inlineStr">
+        <is>
+          <t>https://www.laterre.ca/actualites/bisbille-production-dasclepiade/</t>
+        </is>
+      </c>
+      <c r="F134" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, agricole</t>
+        </is>
+      </c>
+      <c r="G134" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H134" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « agricole ».</t>
+        </is>
+      </c>
+      <c r="I134" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J134" s="64" t="inlineStr">
+        <is>
+          <t>Presse et milieu agricoles. Se rendre disponible comme source sur la filière.</t>
+        </is>
+      </c>
+      <c r="K134" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L134" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M134" s="64" t="inlineStr"/>
+      <c r="N134" s="66" t="n">
+        <v>26</v>
+      </c>
+      <c r="O134" s="66" t="n">
+        <v>18</v>
+      </c>
+      <c r="P134" s="66" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q134" s="66" t="n">
+        <v>11</v>
+      </c>
+      <c r="R134" s="64" t="inlineStr">
+        <is>
+          <t>À qualifier</t>
+        </is>
+      </c>
+      <c r="S134" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T134" s="70" t="inlineStr">
+        <is>
+          <t>À ouvrir à la main</t>
+        </is>
+      </c>
+      <c r="U134" s="64" t="inlineStr">
+        <is>
+          <t>Le serveur refuse les requêtes automatisées. À ouvrir à la main (HTTP 403)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="62" customHeight="1" s="29">
+      <c r="A135" s="66" t="n">
+        <v>118</v>
+      </c>
+      <c r="B135" s="67">
+        <f>SUM(N135:Q135)</f>
+        <v/>
+      </c>
+      <c r="C135" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D135" s="62" t="inlineStr">
+        <is>
+          <t>Silo 57</t>
+        </is>
+      </c>
+      <c r="E135" s="63" t="inlineStr">
+        <is>
+          <t>https://www.silo57.ca/quoi-faire-marches-de-noel-quebec-montreal-cadeaux-liste-ultime</t>
+        </is>
+      </c>
+      <c r="F135" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, media</t>
+        </is>
+      </c>
+      <c r="G135" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H135" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « media ».</t>
+        </is>
+      </c>
+      <c r="I135" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J135" s="64" t="inlineStr">
+        <is>
+          <t>Média grand public. Viser l'inclusion dans un guide saisonnier.</t>
+        </is>
+      </c>
+      <c r="K135" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L135" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M135" s="64" t="inlineStr"/>
+      <c r="N135" s="66" t="n">
+        <v>20</v>
+      </c>
+      <c r="O135" s="66" t="n">
+        <v>15</v>
+      </c>
+      <c r="P135" s="66" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q135" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="R135" s="64" t="inlineStr">
+        <is>
+          <t>À qualifier</t>
+        </is>
+      </c>
+      <c r="S135" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T135" s="70" t="inlineStr">
+        <is>
+          <t>À ouvrir à la main</t>
+        </is>
+      </c>
+      <c r="U135" s="64" t="inlineStr">
+        <is>
+          <t>Le serveur refuse les requêtes automatisées. À ouvrir à la main (HTTP 403)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="62" customHeight="1" s="29">
+      <c r="A136" s="66" t="n">
+        <v>86</v>
+      </c>
+      <c r="B136" s="67">
+        <f>SUM(N136:Q136)</f>
+        <v/>
+      </c>
+      <c r="C136" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D136" s="62" t="inlineStr">
+        <is>
+          <t>Monarch Joint Venture (blogue)</t>
+        </is>
+      </c>
+      <c r="E136" s="63" t="inlineStr">
+        <is>
+          <t>https://monarchjointventure.org/blog/more-than-monarchs-the-untold-story-of-milkweed</t>
+        </is>
+      </c>
+      <c r="F136" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, conservation EN</t>
+        </is>
+      </c>
+      <c r="G136" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H136" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « conservation EN ».</t>
+        </is>
+      </c>
+      <c r="I136" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J136" s="64" t="inlineStr">
+        <is>
+          <t>Angle mission et conservation. Partenariat avant lien.</t>
+        </is>
+      </c>
+      <c r="K136" s="64" t="inlineStr">
+        <is>
+          <t>info@monarchjointventure.org</t>
+        </is>
+      </c>
+      <c r="L136" s="64" t="inlineStr">
+        <is>
+          <t>Confirmé (trouvé sur la page)</t>
+        </is>
+      </c>
+      <c r="M136" s="64" t="inlineStr"/>
+      <c r="N136" s="66" t="n">
+        <v>26</v>
+      </c>
+      <c r="O136" s="66" t="n">
+        <v>22</v>
+      </c>
+      <c r="P136" s="66" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q136" s="66" t="n">
+        <v>12</v>
+      </c>
+      <c r="R136" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S136" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T136" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U136" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="62" customHeight="1" s="29">
+      <c r="A137" s="66" t="n">
+        <v>42</v>
+      </c>
+      <c r="B137" s="67">
+        <f>SUM(N137:Q137)</f>
+        <v/>
+      </c>
+      <c r="C137" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D137" s="62" t="inlineStr">
+        <is>
+          <t>Britannica (milkweed floss)</t>
+        </is>
+      </c>
+      <c r="E137" s="63" t="inlineStr">
+        <is>
+          <t>https://www.britannica.com/topic/milkweed-floss</t>
+        </is>
+      </c>
+      <c r="F137" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, encyclopedie EN</t>
+        </is>
+      </c>
+      <c r="G137" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H137" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « encyclopedie EN ».</t>
+        </is>
+      </c>
+      <c r="I137" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J137" s="64" t="inlineStr">
+        <is>
+          <t>Même règle que pour Wikipédia. Viser la citation, jamais l'ajout direct.</t>
+        </is>
+      </c>
+      <c r="K137" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L137" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M137" s="64" t="inlineStr"/>
+      <c r="N137" s="66" t="n">
+        <v>27</v>
+      </c>
+      <c r="O137" s="66" t="n">
+        <v>25</v>
+      </c>
+      <c r="P137" s="66" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q137" s="66" t="n">
+        <v>13</v>
+      </c>
+      <c r="R137" s="64" t="inlineStr">
+        <is>
+          <t>À qualifier</t>
+        </is>
+      </c>
+      <c r="S137" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T137" s="70" t="inlineStr">
+        <is>
+          <t>À ouvrir à la main</t>
+        </is>
+      </c>
+      <c r="U137" s="64" t="inlineStr">
+        <is>
+          <t>Le serveur refuse les requêtes automatisées. À ouvrir à la main (HTTP 403)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="62" customHeight="1" s="29">
+      <c r="A138" s="66" t="n">
+        <v>87</v>
+      </c>
+      <c r="B138" s="67">
+        <f>SUM(N138:Q138)</f>
+        <v/>
+      </c>
+      <c r="C138" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D138" s="62" t="inlineStr">
+        <is>
+          <t>Nature Up North</t>
+        </is>
+      </c>
+      <c r="E138" s="63" t="inlineStr">
+        <is>
+          <t>https://www.natureupnorth.org/justmynature/paul-j-hetzler/multi-purpose-milkweed</t>
+        </is>
+      </c>
+      <c r="F138" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, conservation EN</t>
+        </is>
+      </c>
+      <c r="G138" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H138" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « conservation EN ».</t>
+        </is>
+      </c>
+      <c r="I138" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J138" s="64" t="inlineStr">
+        <is>
+          <t>Angle mission et conservation. Partenariat avant lien.</t>
+        </is>
+      </c>
+      <c r="K138" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L138" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M138" s="64" t="inlineStr"/>
+      <c r="N138" s="66" t="n">
+        <v>26</v>
+      </c>
+      <c r="O138" s="66" t="n">
+        <v>22</v>
+      </c>
+      <c r="P138" s="66" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q138" s="66" t="n">
+        <v>12</v>
+      </c>
+      <c r="R138" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S138" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T138" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U138" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="62" customHeight="1" s="29">
+      <c r="A139" s="68" t="n">
+        <v>131</v>
+      </c>
+      <c r="B139" s="69">
+        <f>SUM(N139:Q139)</f>
+        <v/>
+      </c>
+      <c r="C139" s="69" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D139" s="62" t="inlineStr">
+        <is>
+          <t>Countryside (iamcountryside)</t>
+        </is>
+      </c>
+      <c r="E139" s="63" t="inlineStr">
+        <is>
+          <t>https://www.iamcountryside.com/growing/milkweed-plant-wild-vegetable/</t>
+        </is>
+      </c>
+      <c r="F139" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, media EN</t>
+        </is>
+      </c>
+      <c r="G139" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H139" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « media EN ».</t>
+        </is>
+      </c>
+      <c r="I139" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J139" s="64" t="inlineStr">
+        <is>
+          <t>Média anglophone. Offrir la ressource en version anglaise.</t>
+        </is>
+      </c>
+      <c r="K139" s="64" t="inlineStr">
+        <is>
+          <t>dmdox07@gmail.com</t>
+        </is>
+      </c>
+      <c r="L139" s="64" t="inlineStr">
+        <is>
+          <t>Confirmé (trouvé sur la page)</t>
+        </is>
+      </c>
+      <c r="M139" s="64" t="inlineStr"/>
+      <c r="N139" s="68" t="n">
+        <v>22</v>
+      </c>
+      <c r="O139" s="68" t="n">
+        <v>14</v>
+      </c>
+      <c r="P139" s="68" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q139" s="68" t="n">
+        <v>9</v>
+      </c>
+      <c r="R139" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S139" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T139" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U139" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="62" customHeight="1" s="29">
+      <c r="A140" s="68" t="n">
+        <v>132</v>
+      </c>
+      <c r="B140" s="69">
+        <f>SUM(N140:Q140)</f>
+        <v/>
+      </c>
+      <c r="C140" s="69" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D140" s="62" t="inlineStr">
+        <is>
+          <t>Kane County Connects</t>
+        </is>
+      </c>
+      <c r="E140" s="63" t="inlineStr">
+        <is>
+          <t>https://kanecountyconnects.com/article/milkweedfloss-milkweed-monarchbutterly-environment-kanecounty</t>
+        </is>
+      </c>
+      <c r="F140" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, media EN</t>
+        </is>
+      </c>
+      <c r="G140" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H140" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « media EN ».</t>
+        </is>
+      </c>
+      <c r="I140" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J140" s="64" t="inlineStr">
+        <is>
+          <t>Média anglophone. Offrir la ressource en version anglaise.</t>
+        </is>
+      </c>
+      <c r="K140" s="64" t="inlineStr">
+        <is>
+          <t>potto@stcparks.org</t>
+        </is>
+      </c>
+      <c r="L140" s="64" t="inlineStr">
+        <is>
+          <t>Confirmé (trouvé sur la page)</t>
+        </is>
+      </c>
+      <c r="M140" s="64" t="inlineStr"/>
+      <c r="N140" s="68" t="n">
+        <v>22</v>
+      </c>
+      <c r="O140" s="68" t="n">
+        <v>14</v>
+      </c>
+      <c r="P140" s="68" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q140" s="68" t="n">
+        <v>9</v>
+      </c>
+      <c r="R140" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S140" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T140" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U140" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="62" customHeight="1" s="29">
+      <c r="A141" s="66" t="n">
+        <v>119</v>
+      </c>
+      <c r="B141" s="67">
+        <f>SUM(N141:Q141)</f>
+        <v/>
+      </c>
+      <c r="C141" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D141" s="62" t="inlineStr">
+        <is>
+          <t>Christian Science Monitor</t>
+        </is>
+      </c>
+      <c r="E141" s="63" t="inlineStr">
+        <is>
+          <t>https://www.csmonitor.com/The-Culture/Gardening/2008/1026/the-heroic-milkweed</t>
+        </is>
+      </c>
+      <c r="F141" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, presse EN</t>
+        </is>
+      </c>
+      <c r="G141" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H141" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « presse EN ».</t>
+        </is>
+      </c>
+      <c r="I141" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J141" s="64" t="inlineStr">
+        <is>
+          <t>Article ancien. Se positionner comme source pour un suivi.</t>
+        </is>
+      </c>
+      <c r="K141" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L141" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M141" s="64" t="inlineStr"/>
+      <c r="N141" s="66" t="n">
+        <v>22</v>
+      </c>
+      <c r="O141" s="66" t="n">
+        <v>24</v>
+      </c>
+      <c r="P141" s="66" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q141" s="66" t="n">
+        <v>11</v>
+      </c>
+      <c r="R141" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S141" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T141" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U141" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="62" customHeight="1" s="29">
+      <c r="A142" s="66" t="n">
+        <v>60</v>
+      </c>
+      <c r="B142" s="67">
+        <f>SUM(N142:Q142)</f>
+        <v/>
+      </c>
+      <c r="C142" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D142" s="62" t="inlineStr">
+        <is>
+          <t>Latulippe (fiche Quartz asclépiade)</t>
+        </is>
+      </c>
+      <c r="E142" s="63" t="inlineStr">
+        <is>
+          <t>https://latulippe.com/en/product/533200/women-s-milkweed-genia-coat/</t>
+        </is>
+      </c>
+      <c r="F142" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, detaillant</t>
+        </is>
+      </c>
+      <c r="G142" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H142" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « detaillant ».</t>
+        </is>
+      </c>
+      <c r="I142" s="64" t="inlineStr">
+        <is>
+          <t>Page d'accueil + collection manteaux</t>
+        </is>
+      </c>
+      <c r="J142" s="64" t="inlineStr">
+        <is>
+          <t>Détaillant qui vend déjà de l'asclépiade. Prospection commerciale d'abord, lien ensuite.</t>
+        </is>
+      </c>
+      <c r="K142" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L142" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M142" s="64" t="inlineStr"/>
+      <c r="N142" s="66" t="n">
+        <v>24</v>
+      </c>
+      <c r="O142" s="66" t="n">
+        <v>17</v>
+      </c>
+      <c r="P142" s="66" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q142" s="66" t="n">
+        <v>14</v>
+      </c>
+      <c r="R142" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S142" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T142" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U142" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="62" customHeight="1" s="29">
+      <c r="A143" s="66" t="n">
+        <v>61</v>
+      </c>
+      <c r="B143" s="67">
+        <f>SUM(N143:Q143)</f>
+        <v/>
+      </c>
+      <c r="C143" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D143" s="62" t="inlineStr">
+        <is>
+          <t>L'Orignal Fringant</t>
+        </is>
+      </c>
+      <c r="E143" s="63" t="inlineStr">
+        <is>
+          <t>https://orignalfringant.ca/boutique/fr/bilodeau-canada/bilodeau-mitaines-de-ville-loup-marin-naturel-et-doublure-asclepiade-p905/</t>
+        </is>
+      </c>
+      <c r="F143" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, detaillant</t>
+        </is>
+      </c>
+      <c r="G143" s="64" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="H143" s="64" t="inlineStr">
+        <is>
+          <t>Page sur l'asclépiade, famille « detaillant ».</t>
+        </is>
+      </c>
+      <c r="I143" s="64" t="inlineStr">
+        <is>
+          <t>Page d'accueil + collection manteaux</t>
+        </is>
+      </c>
+      <c r="J143" s="64" t="inlineStr">
+        <is>
+          <t>Détaillant qui vend déjà de l'asclépiade. Prospection commerciale d'abord, lien ensuite.</t>
+        </is>
+      </c>
+      <c r="K143" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="L143" s="64" t="inlineStr">
+        <is>
+          <t>À trouver</t>
+        </is>
+      </c>
+      <c r="M143" s="64" t="inlineStr"/>
+      <c r="N143" s="66" t="n">
+        <v>24</v>
+      </c>
+      <c r="O143" s="66" t="n">
+        <v>17</v>
+      </c>
+      <c r="P143" s="66" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q143" s="66" t="n">
+        <v>14</v>
+      </c>
+      <c r="R143" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S143" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T143" s="62" t="inlineStr">
+        <is>
+          <t>NON, aucune mention ni lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U143" s="64" t="inlineStr">
+        <is>
+          <t>Proposer une ressource utile avant de parler de lien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="62" customHeight="1" s="29">
+      <c r="A144" s="66" t="n">
+        <v>29</v>
+      </c>
+      <c r="B144" s="67">
+        <f>SUM(N144:Q144)</f>
+        <v/>
+      </c>
+      <c r="C144" s="67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D144" s="62" t="inlineStr">
+        <is>
+          <t>Le Soleil (Lasclay, déc. 2025)</t>
+        </is>
+      </c>
+      <c r="E144" s="63" t="inlineStr">
+        <is>
+          <t>https://www.lesoleil.com/affaires/affaires-locales/2025/12/01/lasclay-devant-le-dilemme-de-fabriquer-au-quebec-QDRJRZ4NNNGLTI5EOEXQB5BVS4/</t>
+        </is>
+      </c>
+      <c r="F144" s="64" t="inlineStr">
+        <is>
+          <t>Vague 2, presse</t>
+        </is>
+      </c>
+      <c r="G144" s="64" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="H144" s="64" t="inlineStr">
+        <is>
+          <t>La page nomme Lasclay.</t>
+        </is>
+      </c>
+      <c r="I144" s="64" t="inlineStr">
+        <is>
+          <t>Page pilier asclépiade</t>
+        </is>
+      </c>
+      <c r="J144" s="64" t="inlineStr">
+        <is>
+          <t>Article sur la filière. Se rendre disponible comme source pour la prochaine couverture, en écrivant directement à la ou au signataire.</t>
+        </is>
+      </c>
+      <c r="K144" s="64" t="inlineStr">
+        <is>
+          <t>cpouliot@lesoleil.com</t>
+        </is>
+      </c>
+      <c r="L144" s="64" t="inlineStr">
+        <is>
+          <t>Confirmé (trouvé sur la page)</t>
+        </is>
+      </c>
+      <c r="M144" s="64" t="inlineStr"/>
+      <c r="N144" s="66" t="n">
+        <v>25</v>
+      </c>
+      <c r="O144" s="66" t="n">
+        <v>21</v>
+      </c>
+      <c r="P144" s="66" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q144" s="66" t="n">
+        <v>14</v>
+      </c>
+      <c r="R144" s="64" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="S144" s="64" t="inlineStr">
+        <is>
+          <t>Ajouté et vérifié le 3 août 2026.</t>
+        </is>
+      </c>
+      <c r="T144" s="71" t="inlineStr">
+        <is>
+          <t>NON, mention présente sans lien (vérifié le 3 août 2026)</t>
+        </is>
+      </c>
+      <c r="U144" s="64" t="inlineStr">
+        <is>
+          <t>Occasion confirmée. Demander l'ajout du lien sur la mention existante.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:U84"/>
+  <autoFilter ref="A4:U144"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A1:S1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="R5:R76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"À contacter,Courriel envoyé,Relancé,Réponse reçue,Lien obtenu,Refusé,Abandonné"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation sqref="R5:R76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"À contacter,Courriel envoyé,Relancé,Réponse reçue,Lien obtenu,Refusé,Abandonné"</formula1>
+    </dataValidation>
+    <dataValidation sqref="R5:R144" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"À contacter,À qualifier,Courriel envoyé,Relancé,Réponse reçue,Lien obtenu,Refusé,Abandonné"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -8712,6 +14215,66 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId140"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -8725,7 +14288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="28" min="1" max="1"/>
@@ -8972,6 +14535,78 @@
       <c r="B31" s="50" t="inlineStr">
         <is>
           <t>Le guide de plantation de l'asclépiade est rédigé et attend l'approbation humaine puis la mise en ligne. Tant qu'il n'est pas publié, 15 lignes restent bloquées : elles promettent une ressource qui n'existe pas encore.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="72" t="inlineStr">
+        <is>
+          <t>AUDIT EXHAUSTIF, 3 août 2026</t>
+        </is>
+      </c>
+      <c r="B33" s="73" t="inlineStr">
+        <is>
+          <t>Deuxième passe complète, menée avec accès réseau. Chaque URL de la liste a été chargée pour de vrai et analysée : présence d'un lien vers lasclay.com, présence du mot Lasclay dans le texte, et adresses de contact exposées sur la page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="74" t="inlineStr">
+        <is>
+          <t>Ce qui a été ratissé</t>
+        </is>
+      </c>
+      <c r="B34" s="73" t="inlineStr">
+        <is>
+          <t>Angles couverts, chacun par plusieurs requêtes : la marque Lasclay et ses fondateurs ; l'asclépiade comme fibre et isolant ; la filière agricole et ses producteurs ; le monarque et la conservation ; les municipalités Ville amie des monarques ; l'asclépiade comestible et la cueillette sauvage ; l'usage médicinal et l'herboristerie ; le miel et l'apiculture ; l'artisanat, le papier et le filage ; l'histoire, le patrimoine et l'usage autochtone ; la recherche universitaire et les centres de transfert ; l'isolation acoustique et le bâtiment ; les répertoires d'achat local et de cadeaux corporatifs ; les détaillants de plein air ; les concurrents et voisins de filière (Quartz Co, Vegeto, Bilodeau, Monark, Encore 3, Protec-Style) ; et le marché anglophone nord-américain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="74" t="inlineStr">
+        <is>
+          <t>Résultats</t>
+        </is>
+      </c>
+      <c r="B35" s="73" t="inlineStr">
+        <is>
+          <t>140 occasions au total. 11 pages portent déjà un lien vers lasclay.com et n'ont donc rien à demander. 35 courriels sont confirmés, dont ceux de journalistes qui ont signé des articles sur Lasclay, ce qui débloque le gisement presse. 22 pages refusent les requêtes automatisées, quel que soit le client utilisé.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="74" t="inlineStr">
+        <is>
+          <t>La limite qui reste</t>
+        </is>
+      </c>
+      <c r="B36" s="73" t="inlineStr">
+        <is>
+          <t>Vingt-deux pages sont protégées par un pare-feu applicatif (Le Devoir, Espaces, La Terre de chez nous, Espace pour la vie, Fondation David Suzuki, Britannica, Sépaq, entre autres). Ni un client HTTP ni un vrai navigateur ne les ouvre depuis ici. Elles sont marquées « À ouvrir à la main » en rouge. Une personne les vérifie toutes en une dizaine de minutes dans son navigateur. Deux domaines de l'audit initial se sont révélés morts au DNS : fibershed.uqam.ca et axedumalt.com.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="74" t="inlineStr">
+        <is>
+          <t>Le filon municipal</t>
+        </is>
+      </c>
+      <c r="B37" s="73" t="inlineStr">
+        <is>
+          <t>Plus de cent municipalités québécoises sont certifiées Ville amie des monarques et publient une page sur l'asclépiade. Sept figurent ici à titre d'échantillon. Une fois le guide de plantation publié, la même offre peut être envoyée à toutes : c'est le gisement le plus reproductible de l'audit, et le moins exploité.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="74" t="inlineStr">
+        <is>
+          <t>Ce qui n'a rien donné</t>
+        </is>
+      </c>
+      <c r="B38" s="73" t="inlineStr">
+        <is>
+          <t>Les balados, les forums et les réseaux sociaux ne produisent pas de lien exploitable sur ces termes. Les recherches y ont été menées et sont restées vides. C'est une information utile : n'y investissez pas de temps pour du lien.</t>
         </is>
       </c>
     </row>
